--- a/pricing/assembly-hours-starter.xlsx
+++ b/pricing/assembly-hours-starter.xlsx
@@ -12,14 +12,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="427">
-  <si>
-    <t>STARTER ASSEMBLY HOURS — every shipped starter (168). Your top-30 commercial list first, then the top-30 residential, then the rest. Type YELLOW 'MY HOURS' per assembly (one installed). 'Hours now' is what ships today (blank = not set). Leave blank to keep it. Send the file back to Track A — do NOT edit hours in the app for this.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="463">
+  <si>
+    <t>STARTER ASSEMBLY HOURS — every starter (183, 1 HELD, 15 NEW since the last version — filter the 'New' column). Your top-30 commercial list first, then the top-30 residential, then the rest. Type YELLOW 'MY HOURS' per assembly (one installed). 'Hours now' is what ships today (blank = not set). Leave blank to keep it. Grey = HELD, leave blank. Send the file back to Track A — do NOT edit hours in the app for this.</t>
   </si>
   <si>
     <t>#</t>
   </si>
   <si>
+    <t>New</t>
+  </si>
+  <si>
     <t>Top-30 list</t>
   </si>
   <si>
@@ -821,6 +824,36 @@
     <t>Surface raceway receptacle (block wall)</t>
   </si>
   <si>
+    <t>HELD - no 700 plate yet. Not seeded until the catalog has: Surface raceway device plate, 700 series. Leave MY HOURS blank.</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>GC5</t>
+  </si>
+  <si>
+    <t>120V feed for door hardware / access control</t>
+  </si>
+  <si>
+    <t>GR1</t>
+  </si>
+  <si>
+    <t>Single-pole switch, old work</t>
+  </si>
+  <si>
+    <t>GR6</t>
+  </si>
+  <si>
+    <t>Kitchen countertop 20A circuit</t>
+  </si>
+  <si>
+    <t>GR7</t>
+  </si>
+  <si>
+    <t>Bathroom 20A circuit</t>
+  </si>
+  <si>
     <t>CS3</t>
   </si>
   <si>
@@ -1019,6 +1052,24 @@
     <t>Time clock and lighting contactor</t>
   </si>
   <si>
+    <t>GC1</t>
+  </si>
+  <si>
+    <t>Emergency battery pack added to a troffer</t>
+  </si>
+  <si>
+    <t>GC3</t>
+  </si>
+  <si>
+    <t>Site / parking lot pole light</t>
+  </si>
+  <si>
+    <t>GC4</t>
+  </si>
+  <si>
+    <t>Emergency light, remote head</t>
+  </si>
+  <si>
     <t>LT3</t>
   </si>
   <si>
@@ -1115,6 +1166,24 @@
     <t>Track light, 8 ft with 4 heads</t>
   </si>
   <si>
+    <t>LT31</t>
+  </si>
+  <si>
+    <t>Wafer LED downlight, 2" (canless)</t>
+  </si>
+  <si>
+    <t>LT32</t>
+  </si>
+  <si>
+    <t>Wafer LED downlight, 8" (canless)</t>
+  </si>
+  <si>
+    <t>LT33</t>
+  </si>
+  <si>
+    <t>Recessed can retrofit, 4"</t>
+  </si>
+  <si>
     <t>CS11</t>
   </si>
   <si>
@@ -1181,6 +1250,36 @@
     <t>Video doorbell wiring</t>
   </si>
   <si>
+    <t>GC2</t>
+  </si>
+  <si>
+    <t>Panelboard replacement, 3-phase, existing feeders</t>
+  </si>
+  <si>
+    <t>GR2</t>
+  </si>
+  <si>
+    <t>Service upgrade 200A, underground</t>
+  </si>
+  <si>
+    <t>GR3</t>
+  </si>
+  <si>
+    <t>Service 320A / 400A residential (two 200A panels)</t>
+  </si>
+  <si>
+    <t>GR4</t>
+  </si>
+  <si>
+    <t>Generator inlet and interlock, 50A</t>
+  </si>
+  <si>
+    <t>GR5</t>
+  </si>
+  <si>
+    <t>Detached garage / shop feeder and panel</t>
+  </si>
+  <si>
     <t>PG1</t>
   </si>
   <si>
@@ -1281,6 +1380,15 @@
   </si>
   <si>
     <t>Your top-30 commercial list, then the top-30 residential list (references/top-assemblies-draft.md), then every other starter by category.</t>
+  </si>
+  <si>
+    <t>15 rows say NEW: starters added since the version this was compared with (ah-previous.xlsx). Filter the 'New' column to see only them.</t>
+  </si>
+  <si>
+    <t>HELD</t>
+  </si>
+  <si>
+    <t>DV34 Surface raceway receptacle (block wall) — grey, and refuses input. It is listed so the sheet is complete, but it is not seeded yet; leave it blank. See its Notes.</t>
   </si>
   <si>
     <t>Not in this sheet</t>
@@ -1311,7 +1419,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1321,6 +1429,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1336,13 +1454,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1685,21 +1805,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I170"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="52" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="40" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1711,8 +1832,9 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1740,14 +1862,14 @@
       <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
@@ -1760,20 +1882,20 @@
       <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -1781,20 +1903,20 @@
       <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -1802,125 +1924,125 @@
       <c r="F5" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>
@@ -1928,78 +2050,78 @@
       <c r="F11" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>42</v>
-      </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
-        <v>45</v>
-      </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
-        <v>51</v>
-      </c>
       <c r="C15" t="s">
         <v>52</v>
       </c>
@@ -2007,214 +2129,214 @@
         <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
-        <v>55</v>
-      </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
-        <v>58</v>
-      </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
-        <v>67</v>
-      </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s">
-        <v>69</v>
-      </c>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G20" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
-      </c>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
-        <v>79</v>
-      </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
-      </c>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G24" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="E25" t="s">
         <v>84</v>
@@ -2222,20 +2344,20 @@
       <c r="F25" t="s">
         <v>85</v>
       </c>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
         <v>88</v>
@@ -2243,104 +2365,104 @@
       <c r="F26" t="s">
         <v>89</v>
       </c>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F27" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G27" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
-        <v>93</v>
-      </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="F28" t="s">
-        <v>95</v>
-      </c>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>96</v>
+      </c>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
-        <v>96</v>
-      </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="F29" t="s">
-        <v>98</v>
-      </c>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G29" t="s">
+        <v>99</v>
+      </c>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
-        <v>99</v>
-      </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="F30" t="s">
-        <v>101</v>
-      </c>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="G30" t="s">
+        <v>102</v>
+      </c>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
-        <v>102</v>
-      </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
         <v>104</v>
@@ -2348,240 +2470,240 @@
       <c r="F31" t="s">
         <v>105</v>
       </c>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G31" t="s">
+        <v>106</v>
+      </c>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
-        <v>106</v>
-      </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F32" t="s">
-        <v>108</v>
-      </c>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G32" t="s">
+        <v>109</v>
+      </c>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" t="s">
-        <v>109</v>
-      </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="F33" t="s">
-        <v>111</v>
-      </c>
-      <c r="G33">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33">
         <v>0.75</v>
       </c>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
-        <v>112</v>
-      </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
-        <v>114</v>
-      </c>
-      <c r="G34">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>115</v>
+      </c>
+      <c r="H34">
         <v>0.6</v>
       </c>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
-        <v>115</v>
-      </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="F35" t="s">
-        <v>117</v>
-      </c>
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>118</v>
+      </c>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" t="s">
-        <v>118</v>
-      </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="F36" t="s">
-        <v>120</v>
-      </c>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>121</v>
+      </c>
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" t="s">
-        <v>121</v>
-      </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="F37" t="s">
-        <v>123</v>
-      </c>
-      <c r="G37">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37">
         <v>0.9</v>
       </c>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
-      <c r="B38" t="s">
-        <v>124</v>
-      </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="F38" t="s">
-        <v>126</v>
-      </c>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>127</v>
+      </c>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39" t="s">
-        <v>127</v>
-      </c>
       <c r="C39" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="F39" t="s">
-        <v>129</v>
-      </c>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>130</v>
+      </c>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40" t="s">
-        <v>130</v>
-      </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
       <c r="F40" t="s">
-        <v>132</v>
-      </c>
-      <c r="G40">
+        <v>14</v>
+      </c>
+      <c r="G40" t="s">
+        <v>133</v>
+      </c>
+      <c r="H40">
         <v>0.6</v>
       </c>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" t="s">
-        <v>133</v>
-      </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="F41" t="s">
-        <v>135</v>
-      </c>
-      <c r="G41">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>136</v>
+      </c>
+      <c r="H41">
         <v>0.7</v>
       </c>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
-        <v>136</v>
-      </c>
       <c r="C42" t="s">
         <v>137</v>
       </c>
@@ -2589,2720 +2711,3095 @@
         <v>138</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>139</v>
       </c>
       <c r="F42" t="s">
-        <v>139</v>
-      </c>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>140</v>
+      </c>
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
-        <v>140</v>
-      </c>
       <c r="C43" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D43" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="F43" t="s">
-        <v>142</v>
-      </c>
-      <c r="G43">
+        <v>14</v>
+      </c>
+      <c r="G43" t="s">
+        <v>143</v>
+      </c>
+      <c r="H43">
         <v>1.5</v>
       </c>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" t="s">
-        <v>143</v>
-      </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="D44" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="E44" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="F44" t="s">
-        <v>145</v>
-      </c>
-      <c r="G44">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>146</v>
+      </c>
+      <c r="H44">
         <v>1.25</v>
       </c>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
-        <v>146</v>
-      </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="D45" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="F45" t="s">
-        <v>148</v>
-      </c>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G45" t="s">
+        <v>149</v>
+      </c>
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
-      <c r="B46" t="s">
-        <v>149</v>
-      </c>
       <c r="C46" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E46" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="F46" t="s">
-        <v>151</v>
-      </c>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>152</v>
+      </c>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
-      <c r="B47" t="s">
-        <v>152</v>
-      </c>
       <c r="C47" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D47" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E47" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
       <c r="F47" t="s">
-        <v>154</v>
-      </c>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>155</v>
+      </c>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48" t="s">
-        <v>155</v>
-      </c>
       <c r="C48" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D48" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>157</v>
       </c>
       <c r="F48" t="s">
-        <v>157</v>
-      </c>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G48" t="s">
+        <v>158</v>
+      </c>
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" t="s">
-        <v>158</v>
-      </c>
       <c r="C49" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="D49" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="E49" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="F49" t="s">
-        <v>160</v>
-      </c>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G49" t="s">
+        <v>161</v>
+      </c>
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50" t="s">
-        <v>161</v>
-      </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="D50" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E50" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
       <c r="F50" t="s">
-        <v>163</v>
-      </c>
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G50" t="s">
+        <v>164</v>
+      </c>
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" t="s">
-        <v>164</v>
-      </c>
       <c r="C51" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="D51" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="E51" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="F51" t="s">
-        <v>166</v>
-      </c>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G51" t="s">
+        <v>167</v>
+      </c>
+      <c r="I51" s="3"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" t="s">
-        <v>167</v>
-      </c>
       <c r="C52" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="D52" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="E52" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="F52" t="s">
-        <v>169</v>
-      </c>
-      <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I52" s="3"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53" t="s">
-        <v>170</v>
-      </c>
       <c r="C53" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="D53" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="E53" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="F53" t="s">
-        <v>172</v>
-      </c>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G53" t="s">
+        <v>173</v>
+      </c>
+      <c r="I53" s="3"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54" t="s">
-        <v>173</v>
-      </c>
       <c r="C54" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="D54" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>175</v>
       </c>
       <c r="F54" t="s">
-        <v>175</v>
-      </c>
-      <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>176</v>
+      </c>
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55" t="s">
-        <v>176</v>
-      </c>
       <c r="C55" t="s">
-        <v>52</v>
+        <v>177</v>
       </c>
       <c r="D55" t="s">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="E55" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="F55" t="s">
-        <v>178</v>
-      </c>
-      <c r="H55" s="3"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G55" t="s">
+        <v>179</v>
+      </c>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" t="s">
-        <v>179</v>
-      </c>
       <c r="C56" t="s">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="D56" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="E56" t="s">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="F56" t="s">
-        <v>181</v>
-      </c>
-      <c r="H56" s="3"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G56" t="s">
+        <v>182</v>
+      </c>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" t="s">
-        <v>182</v>
-      </c>
       <c r="C57" t="s">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="D57" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
-        <v>104</v>
+        <v>184</v>
       </c>
       <c r="F57" t="s">
-        <v>184</v>
-      </c>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G57" t="s">
+        <v>185</v>
+      </c>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58" t="s">
-        <v>185</v>
-      </c>
       <c r="C58" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="D58" t="s">
-        <v>186</v>
+        <v>138</v>
       </c>
       <c r="E58" t="s">
-        <v>84</v>
+        <v>187</v>
       </c>
       <c r="F58" t="s">
-        <v>187</v>
-      </c>
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="G58" t="s">
+        <v>188</v>
+      </c>
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>57</v>
       </c>
-      <c r="B59" t="s">
-        <v>188</v>
-      </c>
       <c r="C59" t="s">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="D59" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="E59" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="F59" t="s">
-        <v>190</v>
-      </c>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="G59" t="s">
+        <v>191</v>
+      </c>
+      <c r="I59" s="3"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" t="s">
-        <v>191</v>
-      </c>
       <c r="C60" t="s">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="D60" t="s">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="E60" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="F60" t="s">
-        <v>193</v>
-      </c>
-      <c r="H60" s="3"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="G60" t="s">
+        <v>194</v>
+      </c>
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" t="s">
-        <v>194</v>
-      </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="D61" t="s">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="E61" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="F61" t="s">
-        <v>196</v>
-      </c>
-      <c r="H61" s="3"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="G61" t="s">
+        <v>197</v>
+      </c>
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" t="s">
-        <v>197</v>
-      </c>
       <c r="C62" t="s">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="D62" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="E62" t="s">
-        <v>84</v>
+        <v>199</v>
       </c>
       <c r="F62" t="s">
-        <v>199</v>
-      </c>
-      <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="G62" t="s">
+        <v>200</v>
+      </c>
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>61</v>
       </c>
-      <c r="B63" t="s">
-        <v>200</v>
-      </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D63" t="s">
-        <v>201</v>
+        <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="F63" t="s">
-        <v>202</v>
-      </c>
-      <c r="H63" s="3"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G63" t="s">
+        <v>203</v>
+      </c>
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" t="s">
-        <v>200</v>
-      </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D64" t="s">
-        <v>203</v>
+        <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="F64" t="s">
-        <v>204</v>
-      </c>
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G64" t="s">
+        <v>205</v>
+      </c>
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65" t="s">
-        <v>200</v>
-      </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D65" t="s">
-        <v>205</v>
+        <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="F65" t="s">
-        <v>206</v>
-      </c>
-      <c r="H65" s="3"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G65" t="s">
+        <v>207</v>
+      </c>
+      <c r="I65" s="3"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66" t="s">
-        <v>200</v>
-      </c>
       <c r="C66" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D66" t="s">
-        <v>207</v>
+        <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="F66" t="s">
-        <v>208</v>
-      </c>
-      <c r="H66" s="3"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G66" t="s">
+        <v>209</v>
+      </c>
+      <c r="I66" s="3"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67" t="s">
-        <v>200</v>
-      </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D67" t="s">
-        <v>209</v>
+        <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="F67" t="s">
-        <v>210</v>
-      </c>
-      <c r="H67" s="3"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G67" t="s">
+        <v>211</v>
+      </c>
+      <c r="I67" s="3"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68" t="s">
-        <v>200</v>
-      </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D68" t="s">
-        <v>211</v>
+        <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="F68" t="s">
-        <v>212</v>
-      </c>
-      <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G68" t="s">
+        <v>213</v>
+      </c>
+      <c r="I68" s="3"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" t="s">
-        <v>200</v>
-      </c>
       <c r="C69" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D69" t="s">
-        <v>213</v>
+        <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="F69" t="s">
-        <v>214</v>
-      </c>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G69" t="s">
+        <v>215</v>
+      </c>
+      <c r="I69" s="3"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70" t="s">
-        <v>200</v>
-      </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D70" t="s">
-        <v>215</v>
+        <v>53</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>216</v>
       </c>
       <c r="F70" t="s">
-        <v>216</v>
-      </c>
-      <c r="H70" s="3"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G70" t="s">
+        <v>217</v>
+      </c>
+      <c r="I70" s="3"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>69</v>
       </c>
-      <c r="B71" t="s">
-        <v>200</v>
-      </c>
       <c r="C71" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D71" t="s">
-        <v>217</v>
+        <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="F71" t="s">
-        <v>218</v>
-      </c>
-      <c r="H71" s="3"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G71" t="s">
+        <v>219</v>
+      </c>
+      <c r="I71" s="3"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
-      <c r="B72" t="s">
-        <v>200</v>
-      </c>
       <c r="C72" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D72" t="s">
-        <v>219</v>
+        <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="F72" t="s">
-        <v>220</v>
-      </c>
-      <c r="H72" s="3"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G72" t="s">
+        <v>221</v>
+      </c>
+      <c r="I72" s="3"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
-      <c r="B73" t="s">
-        <v>200</v>
-      </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D73" t="s">
-        <v>221</v>
+        <v>138</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="F73" t="s">
-        <v>222</v>
-      </c>
-      <c r="H73" s="3"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="G73" t="s">
+        <v>223</v>
+      </c>
+      <c r="I73" s="3"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>72</v>
       </c>
-      <c r="B74" t="s">
-        <v>200</v>
-      </c>
       <c r="C74" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D74" t="s">
-        <v>223</v>
+        <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>17</v>
+        <v>224</v>
       </c>
       <c r="F74" t="s">
-        <v>224</v>
-      </c>
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>225</v>
+      </c>
+      <c r="I74" s="3"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" t="s">
-        <v>200</v>
-      </c>
       <c r="C75" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D75" t="s">
-        <v>225</v>
+        <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>17</v>
+        <v>226</v>
       </c>
       <c r="F75" t="s">
-        <v>226</v>
-      </c>
-      <c r="H75" s="3"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>227</v>
+      </c>
+      <c r="I75" s="3"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
-      <c r="B76" t="s">
-        <v>200</v>
-      </c>
       <c r="C76" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D76" t="s">
-        <v>227</v>
+        <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="F76" t="s">
-        <v>228</v>
-      </c>
-      <c r="H76" s="3"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>229</v>
+      </c>
+      <c r="I76" s="3"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" t="s">
-        <v>200</v>
-      </c>
       <c r="C77" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D77" t="s">
-        <v>229</v>
+        <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>230</v>
       </c>
       <c r="F77" t="s">
-        <v>230</v>
-      </c>
-      <c r="H77" s="3"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>231</v>
+      </c>
+      <c r="I77" s="3"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" t="s">
-        <v>200</v>
-      </c>
       <c r="C78" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D78" t="s">
-        <v>231</v>
+        <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>232</v>
       </c>
       <c r="F78" t="s">
-        <v>232</v>
-      </c>
-      <c r="H78" s="3"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>233</v>
+      </c>
+      <c r="I78" s="3"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
-      <c r="B79" t="s">
-        <v>200</v>
-      </c>
       <c r="C79" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D79" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="E79" t="s">
-        <v>17</v>
+        <v>234</v>
       </c>
       <c r="F79" t="s">
-        <v>234</v>
-      </c>
-      <c r="H79" s="3"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>235</v>
+      </c>
+      <c r="I79" s="3"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
-      <c r="B80" t="s">
-        <v>200</v>
-      </c>
       <c r="C80" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D80" t="s">
-        <v>235</v>
+        <v>53</v>
       </c>
       <c r="E80" t="s">
-        <v>17</v>
+        <v>236</v>
       </c>
       <c r="F80" t="s">
-        <v>236</v>
-      </c>
-      <c r="H80" s="3"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>237</v>
+      </c>
+      <c r="I80" s="3"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>79</v>
       </c>
-      <c r="B81" t="s">
-        <v>200</v>
-      </c>
       <c r="C81" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D81" t="s">
-        <v>237</v>
+        <v>138</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>238</v>
       </c>
       <c r="F81" t="s">
-        <v>238</v>
-      </c>
-      <c r="H81" s="3"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>239</v>
+      </c>
+      <c r="I81" s="3"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>80</v>
       </c>
-      <c r="B82" t="s">
-        <v>200</v>
-      </c>
       <c r="C82" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D82" t="s">
-        <v>239</v>
+        <v>53</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>240</v>
       </c>
       <c r="F82" t="s">
-        <v>240</v>
-      </c>
-      <c r="H82" s="3"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>241</v>
+      </c>
+      <c r="I82" s="3"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" t="s">
-        <v>200</v>
-      </c>
       <c r="C83" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D83" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
       <c r="E83" t="s">
-        <v>17</v>
+        <v>242</v>
       </c>
       <c r="F83" t="s">
-        <v>242</v>
-      </c>
-      <c r="H83" s="3"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>243</v>
+      </c>
+      <c r="I83" s="3"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" t="s">
-        <v>200</v>
-      </c>
       <c r="C84" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D84" t="s">
-        <v>243</v>
+        <v>53</v>
       </c>
       <c r="E84" t="s">
-        <v>17</v>
+        <v>244</v>
       </c>
       <c r="F84" t="s">
-        <v>244</v>
-      </c>
-      <c r="H84" s="3"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>245</v>
+      </c>
+      <c r="I84" s="3"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>83</v>
       </c>
-      <c r="B85" t="s">
-        <v>200</v>
-      </c>
       <c r="C85" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D85" t="s">
-        <v>245</v>
+        <v>53</v>
       </c>
       <c r="E85" t="s">
-        <v>17</v>
+        <v>246</v>
       </c>
       <c r="F85" t="s">
-        <v>246</v>
-      </c>
-      <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>247</v>
+      </c>
+      <c r="I85" s="3"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>84</v>
       </c>
-      <c r="B86" t="s">
-        <v>200</v>
-      </c>
       <c r="C86" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D86" t="s">
-        <v>247</v>
+        <v>53</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>248</v>
       </c>
       <c r="F86" t="s">
-        <v>248</v>
-      </c>
-      <c r="H86" s="3"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>249</v>
+      </c>
+      <c r="I86" s="3"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>85</v>
       </c>
-      <c r="B87" t="s">
-        <v>200</v>
-      </c>
       <c r="C87" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D87" t="s">
-        <v>249</v>
+        <v>53</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>250</v>
       </c>
       <c r="F87" t="s">
-        <v>250</v>
-      </c>
-      <c r="H87" s="3"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>251</v>
+      </c>
+      <c r="I87" s="3"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>86</v>
       </c>
-      <c r="B88" t="s">
-        <v>200</v>
-      </c>
       <c r="C88" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D88" t="s">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>252</v>
       </c>
       <c r="F88" t="s">
-        <v>252</v>
-      </c>
-      <c r="H88" s="3"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>253</v>
+      </c>
+      <c r="I88" s="3"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>87</v>
       </c>
-      <c r="B89" t="s">
-        <v>200</v>
-      </c>
       <c r="C89" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D89" t="s">
-        <v>253</v>
+        <v>138</v>
       </c>
       <c r="E89" t="s">
-        <v>17</v>
+        <v>254</v>
       </c>
       <c r="F89" t="s">
-        <v>254</v>
-      </c>
-      <c r="H89" s="3"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>255</v>
+      </c>
+      <c r="I89" s="3"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>88</v>
       </c>
-      <c r="B90" t="s">
-        <v>200</v>
-      </c>
       <c r="C90" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D90" t="s">
-        <v>255</v>
+        <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>17</v>
+        <v>256</v>
       </c>
       <c r="F90" t="s">
-        <v>256</v>
-      </c>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>257</v>
+      </c>
+      <c r="I90" s="3"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" t="s">
-        <v>200</v>
-      </c>
       <c r="C91" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D91" t="s">
-        <v>257</v>
+        <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>258</v>
       </c>
       <c r="F91" t="s">
-        <v>258</v>
-      </c>
-      <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>259</v>
+      </c>
+      <c r="I91" s="3"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>90</v>
       </c>
-      <c r="B92" t="s">
-        <v>200</v>
-      </c>
       <c r="C92" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D92" t="s">
-        <v>259</v>
+        <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>17</v>
+        <v>260</v>
       </c>
       <c r="F92" t="s">
-        <v>260</v>
-      </c>
-      <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>261</v>
+      </c>
+      <c r="I92" s="3"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>91</v>
       </c>
-      <c r="B93" t="s">
-        <v>200</v>
-      </c>
       <c r="C93" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D93" t="s">
-        <v>261</v>
+        <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>262</v>
       </c>
       <c r="F93" t="s">
-        <v>262</v>
-      </c>
-      <c r="H93" s="3"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>263</v>
+      </c>
+      <c r="I93" s="3"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>92</v>
       </c>
-      <c r="B94" t="s">
-        <v>200</v>
-      </c>
       <c r="C94" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D94" t="s">
-        <v>263</v>
+        <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c r="F94" t="s">
-        <v>264</v>
-      </c>
-      <c r="H94" s="3"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>265</v>
+      </c>
+      <c r="I94" s="3"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" t="s">
-        <v>200</v>
-      </c>
       <c r="C95" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D95" t="s">
-        <v>265</v>
+        <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>266</v>
       </c>
       <c r="F95" t="s">
-        <v>266</v>
-      </c>
-      <c r="H95" s="3"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>267</v>
+      </c>
+      <c r="I95" s="3"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>94</v>
       </c>
-      <c r="B96" t="s">
-        <v>200</v>
-      </c>
       <c r="C96" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D96" t="s">
-        <v>267</v>
+        <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>17</v>
+        <v>268</v>
       </c>
       <c r="F96" t="s">
-        <v>268</v>
-      </c>
-      <c r="H96" s="3"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>269</v>
+      </c>
+      <c r="I96" s="4"/>
+      <c r="J96" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97" t="s">
-        <v>200</v>
+      <c r="B97" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C97" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>104</v>
+        <v>272</v>
       </c>
       <c r="F97" t="s">
-        <v>270</v>
-      </c>
-      <c r="H97" s="3"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>273</v>
+      </c>
+      <c r="I97" s="3"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98" t="s">
-        <v>200</v>
+      <c r="B98" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C98" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>138</v>
       </c>
       <c r="E98" t="s">
-        <v>104</v>
+        <v>274</v>
       </c>
       <c r="F98" t="s">
-        <v>272</v>
-      </c>
-      <c r="H98" s="3"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>275</v>
+      </c>
+      <c r="I98" s="3"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99" t="s">
-        <v>200</v>
+      <c r="B99" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C99" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D99" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="E99" t="s">
-        <v>104</v>
+        <v>276</v>
       </c>
       <c r="F99" t="s">
-        <v>274</v>
-      </c>
-      <c r="H99" s="3"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>277</v>
+      </c>
+      <c r="I99" s="3"/>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100" t="s">
-        <v>200</v>
+      <c r="B100" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C100" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D100" t="s">
-        <v>275</v>
+        <v>138</v>
       </c>
       <c r="E100" t="s">
-        <v>104</v>
+        <v>278</v>
       </c>
       <c r="F100" t="s">
-        <v>276</v>
-      </c>
-      <c r="H100" s="3"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>279</v>
+      </c>
+      <c r="I100" s="3"/>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" t="s">
-        <v>200</v>
-      </c>
       <c r="C101" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D101" t="s">
-        <v>277</v>
+        <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>104</v>
+        <v>280</v>
       </c>
       <c r="F101" t="s">
-        <v>278</v>
-      </c>
-      <c r="H101" s="3"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G101" t="s">
+        <v>281</v>
+      </c>
+      <c r="I101" s="3"/>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>100</v>
       </c>
-      <c r="B102" t="s">
-        <v>200</v>
-      </c>
       <c r="C102" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D102" t="s">
-        <v>279</v>
+        <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>104</v>
+        <v>282</v>
       </c>
       <c r="F102" t="s">
-        <v>280</v>
-      </c>
-      <c r="H102" s="3"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G102" t="s">
+        <v>283</v>
+      </c>
+      <c r="I102" s="3"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>101</v>
       </c>
-      <c r="B103" t="s">
-        <v>200</v>
-      </c>
       <c r="C103" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D103" t="s">
-        <v>281</v>
+        <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>104</v>
+        <v>284</v>
       </c>
       <c r="F103" t="s">
-        <v>282</v>
-      </c>
-      <c r="H103" s="3"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G103" t="s">
+        <v>285</v>
+      </c>
+      <c r="I103" s="3"/>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>102</v>
       </c>
-      <c r="B104" t="s">
-        <v>200</v>
-      </c>
       <c r="C104" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D104" t="s">
-        <v>283</v>
+        <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>104</v>
+        <v>286</v>
       </c>
       <c r="F104" t="s">
-        <v>284</v>
-      </c>
-      <c r="H104" s="3"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G104" t="s">
+        <v>287</v>
+      </c>
+      <c r="I104" s="3"/>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>103</v>
       </c>
-      <c r="B105" t="s">
-        <v>200</v>
-      </c>
       <c r="C105" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D105" t="s">
-        <v>285</v>
+        <v>138</v>
       </c>
       <c r="E105" t="s">
-        <v>104</v>
+        <v>288</v>
       </c>
       <c r="F105" t="s">
-        <v>286</v>
-      </c>
-      <c r="H105" s="3"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G105" t="s">
+        <v>289</v>
+      </c>
+      <c r="I105" s="3"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>104</v>
       </c>
-      <c r="B106" t="s">
-        <v>200</v>
-      </c>
       <c r="C106" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D106" t="s">
-        <v>287</v>
+        <v>138</v>
       </c>
       <c r="E106" t="s">
-        <v>104</v>
+        <v>290</v>
       </c>
       <c r="F106" t="s">
-        <v>288</v>
-      </c>
-      <c r="H106" s="3"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G106" t="s">
+        <v>291</v>
+      </c>
+      <c r="I106" s="3"/>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>105</v>
       </c>
-      <c r="B107" t="s">
-        <v>200</v>
-      </c>
       <c r="C107" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D107" t="s">
-        <v>289</v>
+        <v>138</v>
       </c>
       <c r="E107" t="s">
-        <v>104</v>
+        <v>292</v>
       </c>
       <c r="F107" t="s">
-        <v>290</v>
-      </c>
-      <c r="H107" s="3"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G107" t="s">
+        <v>293</v>
+      </c>
+      <c r="I107" s="3"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>106</v>
       </c>
-      <c r="B108" t="s">
-        <v>200</v>
-      </c>
       <c r="C108" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D108" t="s">
-        <v>291</v>
+        <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>104</v>
+        <v>294</v>
       </c>
       <c r="F108" t="s">
-        <v>292</v>
-      </c>
-      <c r="H108" s="3"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G108" t="s">
+        <v>295</v>
+      </c>
+      <c r="I108" s="3"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>107</v>
       </c>
-      <c r="B109" t="s">
-        <v>200</v>
-      </c>
       <c r="C109" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D109" t="s">
-        <v>293</v>
+        <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>104</v>
+        <v>296</v>
       </c>
       <c r="F109" t="s">
-        <v>294</v>
-      </c>
-      <c r="H109" s="3"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G109" t="s">
+        <v>297</v>
+      </c>
+      <c r="I109" s="3"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>108</v>
       </c>
-      <c r="B110" t="s">
-        <v>200</v>
-      </c>
       <c r="C110" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D110" t="s">
-        <v>295</v>
+        <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>104</v>
+        <v>298</v>
       </c>
       <c r="F110" t="s">
-        <v>296</v>
-      </c>
-      <c r="H110" s="3"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G110" t="s">
+        <v>299</v>
+      </c>
+      <c r="I110" s="3"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>109</v>
       </c>
-      <c r="B111" t="s">
-        <v>200</v>
-      </c>
       <c r="C111" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D111" t="s">
-        <v>297</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>104</v>
+        <v>300</v>
       </c>
       <c r="F111" t="s">
-        <v>298</v>
-      </c>
-      <c r="H111" s="3"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G111" t="s">
+        <v>301</v>
+      </c>
+      <c r="I111" s="3"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>110</v>
       </c>
-      <c r="B112" t="s">
-        <v>200</v>
-      </c>
       <c r="C112" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D112" t="s">
-        <v>299</v>
+        <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>104</v>
+        <v>302</v>
       </c>
       <c r="F112" t="s">
-        <v>300</v>
-      </c>
-      <c r="H112" s="3"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G112" t="s">
+        <v>303</v>
+      </c>
+      <c r="I112" s="3"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" t="s">
-        <v>200</v>
-      </c>
       <c r="C113" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D113" t="s">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>104</v>
+        <v>304</v>
       </c>
       <c r="F113" t="s">
-        <v>302</v>
-      </c>
-      <c r="H113" s="3"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G113" t="s">
+        <v>305</v>
+      </c>
+      <c r="I113" s="3"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>112</v>
       </c>
-      <c r="B114" t="s">
-        <v>200</v>
-      </c>
       <c r="C114" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D114" t="s">
-        <v>303</v>
+        <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>104</v>
+        <v>306</v>
       </c>
       <c r="F114" t="s">
-        <v>304</v>
-      </c>
-      <c r="H114" s="3"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G114" t="s">
+        <v>307</v>
+      </c>
+      <c r="I114" s="3"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>113</v>
       </c>
-      <c r="B115" t="s">
-        <v>200</v>
-      </c>
       <c r="C115" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D115" t="s">
-        <v>305</v>
+        <v>138</v>
       </c>
       <c r="E115" t="s">
-        <v>104</v>
+        <v>308</v>
       </c>
       <c r="F115" t="s">
-        <v>306</v>
-      </c>
-      <c r="H115" s="3"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G115" t="s">
+        <v>309</v>
+      </c>
+      <c r="I115" s="3"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>114</v>
       </c>
-      <c r="B116" t="s">
-        <v>200</v>
-      </c>
       <c r="C116" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D116" t="s">
-        <v>307</v>
+        <v>53</v>
       </c>
       <c r="E116" t="s">
-        <v>104</v>
+        <v>310</v>
       </c>
       <c r="F116" t="s">
-        <v>308</v>
-      </c>
-      <c r="H116" s="3"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G116" t="s">
+        <v>311</v>
+      </c>
+      <c r="I116" s="3"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>115</v>
       </c>
-      <c r="B117" t="s">
-        <v>200</v>
-      </c>
       <c r="C117" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D117" t="s">
-        <v>309</v>
+        <v>138</v>
       </c>
       <c r="E117" t="s">
-        <v>104</v>
+        <v>312</v>
       </c>
       <c r="F117" t="s">
-        <v>310</v>
-      </c>
-      <c r="H117" s="3"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G117" t="s">
+        <v>313</v>
+      </c>
+      <c r="I117" s="3"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>116</v>
       </c>
-      <c r="B118" t="s">
-        <v>200</v>
-      </c>
       <c r="C118" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D118" t="s">
-        <v>311</v>
+        <v>138</v>
       </c>
       <c r="E118" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="F118" t="s">
-        <v>312</v>
-      </c>
-      <c r="H118" s="3"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G118" t="s">
+        <v>315</v>
+      </c>
+      <c r="I118" s="3"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>117</v>
       </c>
-      <c r="B119" t="s">
-        <v>200</v>
-      </c>
       <c r="C119" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D119" t="s">
-        <v>313</v>
+        <v>138</v>
       </c>
       <c r="E119" t="s">
-        <v>104</v>
+        <v>316</v>
       </c>
       <c r="F119" t="s">
-        <v>314</v>
-      </c>
-      <c r="H119" s="3"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G119" t="s">
+        <v>317</v>
+      </c>
+      <c r="I119" s="3"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>118</v>
       </c>
-      <c r="B120" t="s">
-        <v>200</v>
-      </c>
       <c r="C120" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D120" t="s">
-        <v>315</v>
+        <v>138</v>
       </c>
       <c r="E120" t="s">
-        <v>104</v>
+        <v>318</v>
       </c>
       <c r="F120" t="s">
-        <v>316</v>
-      </c>
-      <c r="H120" s="3"/>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G120" t="s">
+        <v>319</v>
+      </c>
+      <c r="I120" s="3"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>119</v>
       </c>
-      <c r="B121" t="s">
-        <v>200</v>
-      </c>
       <c r="C121" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D121" t="s">
-        <v>317</v>
+        <v>138</v>
       </c>
       <c r="E121" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="F121" t="s">
-        <v>318</v>
-      </c>
-      <c r="H121" s="3"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G121" t="s">
+        <v>321</v>
+      </c>
+      <c r="I121" s="3"/>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>120</v>
       </c>
-      <c r="B122" t="s">
-        <v>200</v>
-      </c>
       <c r="C122" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D122" t="s">
-        <v>319</v>
+        <v>138</v>
       </c>
       <c r="E122" t="s">
-        <v>40</v>
+        <v>322</v>
       </c>
       <c r="F122" t="s">
-        <v>320</v>
-      </c>
-      <c r="H122" s="3"/>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G122" t="s">
+        <v>323</v>
+      </c>
+      <c r="I122" s="3"/>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" t="s">
-        <v>200</v>
-      </c>
       <c r="C123" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D123" t="s">
-        <v>321</v>
+        <v>138</v>
       </c>
       <c r="E123" t="s">
-        <v>40</v>
+        <v>324</v>
       </c>
       <c r="F123" t="s">
-        <v>322</v>
-      </c>
-      <c r="H123" s="3"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G123" t="s">
+        <v>325</v>
+      </c>
+      <c r="I123" s="3"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>122</v>
       </c>
-      <c r="B124" t="s">
-        <v>200</v>
-      </c>
       <c r="C124" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D124" t="s">
-        <v>323</v>
+        <v>138</v>
       </c>
       <c r="E124" t="s">
-        <v>40</v>
+        <v>326</v>
       </c>
       <c r="F124" t="s">
-        <v>324</v>
-      </c>
-      <c r="H124" s="3"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G124" t="s">
+        <v>327</v>
+      </c>
+      <c r="I124" s="3"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" t="s">
-        <v>200</v>
-      </c>
       <c r="C125" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D125" t="s">
-        <v>325</v>
+        <v>12</v>
       </c>
       <c r="E125" t="s">
-        <v>40</v>
+        <v>328</v>
       </c>
       <c r="F125" t="s">
-        <v>326</v>
-      </c>
-      <c r="H125" s="3"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G125" t="s">
+        <v>329</v>
+      </c>
+      <c r="I125" s="3"/>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>124</v>
       </c>
-      <c r="B126" t="s">
-        <v>200</v>
-      </c>
       <c r="C126" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D126" t="s">
-        <v>327</v>
+        <v>53</v>
       </c>
       <c r="E126" t="s">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="F126" t="s">
-        <v>328</v>
-      </c>
-      <c r="H126" s="3"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G126" t="s">
+        <v>331</v>
+      </c>
+      <c r="I126" s="3"/>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>125</v>
       </c>
-      <c r="B127" t="s">
-        <v>200</v>
-      </c>
       <c r="C127" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D127" t="s">
-        <v>329</v>
+        <v>12</v>
       </c>
       <c r="E127" t="s">
-        <v>40</v>
+        <v>332</v>
       </c>
       <c r="F127" t="s">
-        <v>330</v>
-      </c>
-      <c r="H127" s="3"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G127" t="s">
+        <v>333</v>
+      </c>
+      <c r="I127" s="3"/>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>126</v>
       </c>
-      <c r="B128" t="s">
-        <v>200</v>
-      </c>
       <c r="C128" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D128" t="s">
-        <v>331</v>
+        <v>53</v>
       </c>
       <c r="E128" t="s">
-        <v>40</v>
+        <v>334</v>
       </c>
       <c r="F128" t="s">
-        <v>332</v>
-      </c>
-      <c r="H128" s="3"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G128" t="s">
+        <v>335</v>
+      </c>
+      <c r="I128" s="3"/>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>127</v>
       </c>
-      <c r="B129" t="s">
-        <v>200</v>
-      </c>
       <c r="C129" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D129" t="s">
-        <v>333</v>
+        <v>12</v>
       </c>
       <c r="E129" t="s">
-        <v>13</v>
+        <v>336</v>
       </c>
       <c r="F129" t="s">
-        <v>334</v>
-      </c>
-      <c r="H129" s="3"/>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G129" t="s">
+        <v>337</v>
+      </c>
+      <c r="I129" s="3"/>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>128</v>
       </c>
-      <c r="B130" t="s">
-        <v>200</v>
-      </c>
       <c r="C130" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D130" t="s">
-        <v>335</v>
+        <v>138</v>
       </c>
       <c r="E130" t="s">
-        <v>13</v>
+        <v>338</v>
       </c>
       <c r="F130" t="s">
-        <v>336</v>
-      </c>
-      <c r="H130" s="3"/>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G130" t="s">
+        <v>339</v>
+      </c>
+      <c r="I130" s="3"/>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>129</v>
       </c>
-      <c r="B131" t="s">
-        <v>200</v>
-      </c>
       <c r="C131" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D131" t="s">
-        <v>337</v>
+        <v>53</v>
       </c>
       <c r="E131" t="s">
-        <v>13</v>
+        <v>340</v>
       </c>
       <c r="F131" t="s">
-        <v>338</v>
-      </c>
-      <c r="H131" s="3"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G131" t="s">
+        <v>341</v>
+      </c>
+      <c r="I131" s="3"/>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>130</v>
       </c>
-      <c r="B132" t="s">
-        <v>200</v>
-      </c>
       <c r="C132" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D132" t="s">
-        <v>339</v>
+        <v>53</v>
       </c>
       <c r="E132" t="s">
-        <v>13</v>
+        <v>342</v>
       </c>
       <c r="F132" t="s">
-        <v>340</v>
-      </c>
-      <c r="H132" s="3"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="G132" t="s">
+        <v>343</v>
+      </c>
+      <c r="I132" s="3"/>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>131</v>
       </c>
-      <c r="B133" t="s">
-        <v>200</v>
-      </c>
       <c r="C133" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D133" t="s">
-        <v>341</v>
+        <v>12</v>
       </c>
       <c r="E133" t="s">
-        <v>13</v>
+        <v>344</v>
       </c>
       <c r="F133" t="s">
-        <v>342</v>
-      </c>
-      <c r="H133" s="3"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G133" t="s">
+        <v>345</v>
+      </c>
+      <c r="I133" s="3"/>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>132</v>
       </c>
-      <c r="B134" t="s">
-        <v>200</v>
+      <c r="B134" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C134" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D134" t="s">
-        <v>343</v>
+        <v>12</v>
       </c>
       <c r="E134" t="s">
-        <v>13</v>
+        <v>346</v>
       </c>
       <c r="F134" t="s">
-        <v>344</v>
-      </c>
-      <c r="H134" s="3"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G134" t="s">
+        <v>347</v>
+      </c>
+      <c r="I134" s="3"/>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>133</v>
       </c>
-      <c r="B135" t="s">
-        <v>200</v>
+      <c r="B135" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C135" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D135" t="s">
-        <v>345</v>
+        <v>12</v>
       </c>
       <c r="E135" t="s">
-        <v>13</v>
+        <v>348</v>
       </c>
       <c r="F135" t="s">
-        <v>346</v>
-      </c>
-      <c r="H135" s="3"/>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G135" t="s">
+        <v>349</v>
+      </c>
+      <c r="I135" s="3"/>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>134</v>
       </c>
-      <c r="B136" t="s">
-        <v>200</v>
+      <c r="B136" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C136" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D136" t="s">
-        <v>347</v>
+        <v>12</v>
       </c>
       <c r="E136" t="s">
-        <v>13</v>
+        <v>350</v>
       </c>
       <c r="F136" t="s">
-        <v>348</v>
-      </c>
-      <c r="H136" s="3"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G136" t="s">
+        <v>351</v>
+      </c>
+      <c r="I136" s="3"/>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>135</v>
       </c>
-      <c r="B137" t="s">
-        <v>200</v>
-      </c>
       <c r="C137" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D137" t="s">
-        <v>349</v>
+        <v>138</v>
       </c>
       <c r="E137" t="s">
-        <v>13</v>
+        <v>352</v>
       </c>
       <c r="F137" t="s">
-        <v>350</v>
-      </c>
-      <c r="H137" s="3"/>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G137" t="s">
+        <v>353</v>
+      </c>
+      <c r="I137" s="3"/>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>136</v>
       </c>
-      <c r="B138" t="s">
-        <v>200</v>
-      </c>
       <c r="C138" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D138" t="s">
-        <v>351</v>
+        <v>53</v>
       </c>
       <c r="E138" t="s">
-        <v>13</v>
+        <v>354</v>
       </c>
       <c r="F138" t="s">
-        <v>352</v>
-      </c>
-      <c r="H138" s="3"/>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G138" t="s">
+        <v>355</v>
+      </c>
+      <c r="I138" s="3"/>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>137</v>
       </c>
-      <c r="B139" t="s">
-        <v>200</v>
-      </c>
       <c r="C139" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D139" t="s">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="E139" t="s">
-        <v>13</v>
+        <v>356</v>
       </c>
       <c r="F139" t="s">
-        <v>354</v>
-      </c>
-      <c r="H139" s="3"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G139" t="s">
+        <v>357</v>
+      </c>
+      <c r="I139" s="3"/>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>138</v>
       </c>
-      <c r="B140" t="s">
-        <v>200</v>
-      </c>
       <c r="C140" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D140" t="s">
-        <v>355</v>
+        <v>53</v>
       </c>
       <c r="E140" t="s">
-        <v>13</v>
+        <v>358</v>
       </c>
       <c r="F140" t="s">
-        <v>356</v>
-      </c>
-      <c r="H140" s="3"/>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G140" t="s">
+        <v>359</v>
+      </c>
+      <c r="I140" s="3"/>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>139</v>
       </c>
-      <c r="B141" t="s">
-        <v>200</v>
-      </c>
       <c r="C141" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D141" t="s">
-        <v>357</v>
+        <v>138</v>
       </c>
       <c r="E141" t="s">
-        <v>13</v>
+        <v>360</v>
       </c>
       <c r="F141" t="s">
-        <v>358</v>
-      </c>
-      <c r="H141" s="3"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G141" t="s">
+        <v>361</v>
+      </c>
+      <c r="I141" s="3"/>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>140</v>
       </c>
-      <c r="B142" t="s">
-        <v>200</v>
-      </c>
       <c r="C142" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D142" t="s">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="E142" t="s">
-        <v>13</v>
+        <v>362</v>
       </c>
       <c r="F142" t="s">
-        <v>360</v>
-      </c>
-      <c r="H142" s="3"/>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G142" t="s">
+        <v>363</v>
+      </c>
+      <c r="I142" s="3"/>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>141</v>
       </c>
-      <c r="B143" t="s">
-        <v>200</v>
-      </c>
       <c r="C143" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D143" t="s">
-        <v>361</v>
+        <v>138</v>
       </c>
       <c r="E143" t="s">
-        <v>13</v>
+        <v>364</v>
       </c>
       <c r="F143" t="s">
-        <v>362</v>
-      </c>
-      <c r="H143" s="3"/>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G143" t="s">
+        <v>365</v>
+      </c>
+      <c r="I143" s="3"/>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>142</v>
       </c>
-      <c r="B144" t="s">
-        <v>200</v>
-      </c>
       <c r="C144" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D144" t="s">
-        <v>363</v>
+        <v>138</v>
       </c>
       <c r="E144" t="s">
-        <v>13</v>
+        <v>366</v>
       </c>
       <c r="F144" t="s">
-        <v>364</v>
-      </c>
-      <c r="H144" s="3"/>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G144" t="s">
+        <v>367</v>
+      </c>
+      <c r="I144" s="3"/>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>143</v>
       </c>
-      <c r="B145" t="s">
-        <v>200</v>
-      </c>
       <c r="C145" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D145" t="s">
-        <v>365</v>
+        <v>53</v>
       </c>
       <c r="E145" t="s">
-        <v>13</v>
+        <v>368</v>
       </c>
       <c r="F145" t="s">
-        <v>366</v>
-      </c>
-      <c r="H145" s="3"/>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G145" t="s">
+        <v>369</v>
+      </c>
+      <c r="I145" s="3"/>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>144</v>
       </c>
-      <c r="B146" t="s">
-        <v>200</v>
-      </c>
       <c r="C146" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D146" t="s">
-        <v>367</v>
+        <v>138</v>
       </c>
       <c r="E146" t="s">
-        <v>88</v>
+        <v>370</v>
       </c>
       <c r="F146" t="s">
-        <v>368</v>
-      </c>
-      <c r="H146" s="3"/>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G146" t="s">
+        <v>371</v>
+      </c>
+      <c r="I146" s="3"/>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>145</v>
       </c>
-      <c r="B147" t="s">
-        <v>200</v>
-      </c>
       <c r="C147" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D147" t="s">
-        <v>369</v>
+        <v>138</v>
       </c>
       <c r="E147" t="s">
-        <v>88</v>
+        <v>372</v>
       </c>
       <c r="F147" t="s">
-        <v>370</v>
-      </c>
-      <c r="H147" s="3"/>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G147" t="s">
+        <v>373</v>
+      </c>
+      <c r="I147" s="3"/>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>146</v>
       </c>
-      <c r="B148" t="s">
-        <v>200</v>
-      </c>
       <c r="C148" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D148" t="s">
-        <v>371</v>
+        <v>12</v>
       </c>
       <c r="E148" t="s">
-        <v>88</v>
+        <v>374</v>
       </c>
       <c r="F148" t="s">
-        <v>372</v>
-      </c>
-      <c r="H148" s="3"/>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G148" t="s">
+        <v>375</v>
+      </c>
+      <c r="I148" s="3"/>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>147</v>
       </c>
-      <c r="B149" t="s">
-        <v>200</v>
-      </c>
       <c r="C149" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D149" t="s">
-        <v>373</v>
+        <v>12</v>
       </c>
       <c r="E149" t="s">
-        <v>88</v>
+        <v>376</v>
       </c>
       <c r="F149" t="s">
-        <v>374</v>
-      </c>
-      <c r="H149" s="3"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G149" t="s">
+        <v>377</v>
+      </c>
+      <c r="I149" s="3"/>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>148</v>
       </c>
-      <c r="B150" t="s">
-        <v>200</v>
-      </c>
       <c r="C150" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D150" t="s">
-        <v>375</v>
+        <v>12</v>
       </c>
       <c r="E150" t="s">
-        <v>88</v>
+        <v>378</v>
       </c>
       <c r="F150" t="s">
-        <v>376</v>
-      </c>
-      <c r="H150" s="3"/>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G150" t="s">
+        <v>379</v>
+      </c>
+      <c r="I150" s="3"/>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>149</v>
       </c>
-      <c r="B151" t="s">
-        <v>200</v>
-      </c>
       <c r="C151" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D151" t="s">
-        <v>377</v>
+        <v>12</v>
       </c>
       <c r="E151" t="s">
-        <v>88</v>
+        <v>380</v>
       </c>
       <c r="F151" t="s">
-        <v>378</v>
-      </c>
-      <c r="H151" s="3"/>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G151" t="s">
+        <v>381</v>
+      </c>
+      <c r="I151" s="3"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>150</v>
       </c>
-      <c r="B152" t="s">
-        <v>200</v>
-      </c>
       <c r="C152" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D152" t="s">
-        <v>379</v>
+        <v>12</v>
       </c>
       <c r="E152" t="s">
-        <v>88</v>
+        <v>382</v>
       </c>
       <c r="F152" t="s">
-        <v>380</v>
-      </c>
-      <c r="H152" s="3"/>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G152" t="s">
+        <v>383</v>
+      </c>
+      <c r="I152" s="3"/>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>151</v>
       </c>
-      <c r="B153" t="s">
-        <v>200</v>
+      <c r="B153" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C153" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D153" t="s">
-        <v>381</v>
+        <v>53</v>
       </c>
       <c r="E153" t="s">
-        <v>88</v>
+        <v>384</v>
       </c>
       <c r="F153" t="s">
-        <v>382</v>
-      </c>
-      <c r="H153" s="3"/>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G153" t="s">
+        <v>385</v>
+      </c>
+      <c r="I153" s="3"/>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>152</v>
       </c>
-      <c r="B154" t="s">
-        <v>200</v>
+      <c r="B154" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C154" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D154" t="s">
-        <v>383</v>
+        <v>53</v>
       </c>
       <c r="E154" t="s">
-        <v>88</v>
+        <v>386</v>
       </c>
       <c r="F154" t="s">
-        <v>384</v>
-      </c>
-      <c r="H154" s="3"/>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G154" t="s">
+        <v>387</v>
+      </c>
+      <c r="I154" s="3"/>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>153</v>
       </c>
-      <c r="B155" t="s">
-        <v>200</v>
+      <c r="B155" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C155" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D155" t="s">
-        <v>385</v>
+        <v>53</v>
       </c>
       <c r="E155" t="s">
-        <v>88</v>
+        <v>388</v>
       </c>
       <c r="F155" t="s">
-        <v>386</v>
-      </c>
-      <c r="H155" s="3"/>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G155" t="s">
+        <v>389</v>
+      </c>
+      <c r="I155" s="3"/>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>154</v>
       </c>
-      <c r="B156" t="s">
-        <v>200</v>
-      </c>
       <c r="C156" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D156" t="s">
-        <v>387</v>
+        <v>12</v>
       </c>
       <c r="E156" t="s">
-        <v>88</v>
+        <v>390</v>
       </c>
       <c r="F156" t="s">
-        <v>388</v>
-      </c>
-      <c r="H156" s="3"/>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G156" t="s">
+        <v>391</v>
+      </c>
+      <c r="I156" s="3"/>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>155</v>
       </c>
-      <c r="B157" t="s">
-        <v>200</v>
-      </c>
       <c r="C157" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D157" t="s">
-        <v>389</v>
+        <v>12</v>
       </c>
       <c r="E157" t="s">
-        <v>84</v>
+        <v>392</v>
       </c>
       <c r="F157" t="s">
-        <v>390</v>
-      </c>
-      <c r="G157">
-        <v>8</v>
-      </c>
-      <c r="H157" s="3"/>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G157" t="s">
+        <v>393</v>
+      </c>
+      <c r="I157" s="3"/>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>156</v>
       </c>
-      <c r="B158" t="s">
-        <v>200</v>
-      </c>
       <c r="C158" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D158" t="s">
-        <v>391</v>
+        <v>12</v>
       </c>
       <c r="E158" t="s">
-        <v>84</v>
+        <v>394</v>
       </c>
       <c r="F158" t="s">
-        <v>392</v>
-      </c>
-      <c r="H158" s="3"/>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G158" t="s">
+        <v>395</v>
+      </c>
+      <c r="I158" s="3"/>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>157</v>
       </c>
-      <c r="B159" t="s">
-        <v>200</v>
-      </c>
       <c r="C159" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D159" t="s">
-        <v>393</v>
+        <v>12</v>
       </c>
       <c r="E159" t="s">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="F159" t="s">
-        <v>394</v>
-      </c>
-      <c r="H159" s="3"/>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G159" t="s">
+        <v>397</v>
+      </c>
+      <c r="I159" s="3"/>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>158</v>
       </c>
-      <c r="B160" t="s">
-        <v>200</v>
-      </c>
       <c r="C160" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D160" t="s">
-        <v>395</v>
+        <v>138</v>
       </c>
       <c r="E160" t="s">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="F160" t="s">
-        <v>396</v>
-      </c>
-      <c r="H160" s="3"/>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G160" t="s">
+        <v>399</v>
+      </c>
+      <c r="I160" s="3"/>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>159</v>
       </c>
-      <c r="B161" t="s">
-        <v>200</v>
-      </c>
       <c r="C161" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D161" t="s">
-        <v>397</v>
+        <v>138</v>
       </c>
       <c r="E161" t="s">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="F161" t="s">
-        <v>398</v>
-      </c>
-      <c r="H161" s="3"/>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G161" t="s">
+        <v>401</v>
+      </c>
+      <c r="I161" s="3"/>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>160</v>
       </c>
-      <c r="B162" t="s">
-        <v>200</v>
-      </c>
       <c r="C162" t="s">
-        <v>137</v>
+        <v>201</v>
       </c>
       <c r="D162" t="s">
-        <v>399</v>
+        <v>53</v>
       </c>
       <c r="E162" t="s">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="F162" t="s">
-        <v>400</v>
-      </c>
-      <c r="H162" s="3"/>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G162" t="s">
+        <v>403</v>
+      </c>
+      <c r="I162" s="3"/>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>161</v>
       </c>
-      <c r="B163" t="s">
-        <v>200</v>
-      </c>
       <c r="C163" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D163" t="s">
-        <v>401</v>
+        <v>138</v>
       </c>
       <c r="E163" t="s">
-        <v>84</v>
+        <v>404</v>
       </c>
       <c r="F163" t="s">
-        <v>402</v>
-      </c>
-      <c r="H163" s="3"/>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G163" t="s">
+        <v>405</v>
+      </c>
+      <c r="I163" s="3"/>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>162</v>
       </c>
-      <c r="B164" t="s">
-        <v>200</v>
-      </c>
       <c r="C164" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D164" t="s">
-        <v>403</v>
+        <v>12</v>
       </c>
       <c r="E164" t="s">
-        <v>84</v>
+        <v>406</v>
       </c>
       <c r="F164" t="s">
-        <v>404</v>
-      </c>
-      <c r="H164" s="3"/>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G164" t="s">
+        <v>407</v>
+      </c>
+      <c r="I164" s="3"/>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>163</v>
       </c>
-      <c r="B165" t="s">
-        <v>200</v>
-      </c>
       <c r="C165" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>138</v>
       </c>
       <c r="E165" t="s">
-        <v>84</v>
+        <v>408</v>
       </c>
       <c r="F165" t="s">
-        <v>406</v>
-      </c>
-      <c r="H165" s="3"/>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G165" t="s">
+        <v>409</v>
+      </c>
+      <c r="I165" s="3"/>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>164</v>
       </c>
-      <c r="B166" t="s">
-        <v>200</v>
-      </c>
       <c r="C166" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D166" t="s">
-        <v>407</v>
+        <v>138</v>
       </c>
       <c r="E166" t="s">
-        <v>84</v>
+        <v>410</v>
       </c>
       <c r="F166" t="s">
-        <v>408</v>
-      </c>
-      <c r="H166" s="3"/>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="G166" t="s">
+        <v>411</v>
+      </c>
+      <c r="I166" s="3"/>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>165</v>
       </c>
-      <c r="B167" t="s">
-        <v>200</v>
+      <c r="B167" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C167" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D167" t="s">
-        <v>409</v>
+        <v>12</v>
       </c>
       <c r="E167" t="s">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="F167" t="s">
-        <v>410</v>
-      </c>
-      <c r="H167" s="3"/>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="G167" t="s">
+        <v>413</v>
+      </c>
+      <c r="I167" s="3"/>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>166</v>
       </c>
-      <c r="B168" t="s">
-        <v>200</v>
+      <c r="B168" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C168" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>138</v>
       </c>
       <c r="E168" t="s">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="F168" t="s">
-        <v>412</v>
-      </c>
-      <c r="H168" s="3"/>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="G168" t="s">
+        <v>415</v>
+      </c>
+      <c r="I168" s="3"/>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>167</v>
       </c>
-      <c r="B169" t="s">
-        <v>200</v>
+      <c r="B169" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C169" t="s">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="D169" t="s">
-        <v>413</v>
+        <v>138</v>
       </c>
       <c r="E169" t="s">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="F169" t="s">
-        <v>414</v>
-      </c>
-      <c r="H169" s="3"/>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="G169" t="s">
+        <v>417</v>
+      </c>
+      <c r="I169" s="3"/>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>168</v>
       </c>
-      <c r="B170" t="s">
-        <v>200</v>
+      <c r="B170" s="5" t="s">
+        <v>271</v>
       </c>
       <c r="C170" t="s">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="D170" t="s">
-        <v>415</v>
+        <v>138</v>
       </c>
       <c r="E170" t="s">
-        <v>84</v>
+        <v>418</v>
       </c>
       <c r="F170" t="s">
-        <v>416</v>
-      </c>
-      <c r="H170" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="G170" t="s">
+        <v>419</v>
+      </c>
+      <c r="I170" s="3"/>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C171" t="s">
+        <v>201</v>
+      </c>
+      <c r="D171" t="s">
+        <v>138</v>
+      </c>
+      <c r="E171" t="s">
+        <v>420</v>
+      </c>
+      <c r="F171" t="s">
+        <v>85</v>
+      </c>
+      <c r="G171" t="s">
+        <v>421</v>
+      </c>
+      <c r="I171" s="3"/>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="C172" t="s">
+        <v>201</v>
+      </c>
+      <c r="D172" t="s">
+        <v>53</v>
+      </c>
+      <c r="E172" t="s">
+        <v>422</v>
+      </c>
+      <c r="F172" t="s">
+        <v>85</v>
+      </c>
+      <c r="G172" t="s">
+        <v>423</v>
+      </c>
+      <c r="H172">
+        <v>8</v>
+      </c>
+      <c r="I172" s="3"/>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="C173" t="s">
+        <v>201</v>
+      </c>
+      <c r="D173" t="s">
+        <v>53</v>
+      </c>
+      <c r="E173" t="s">
+        <v>424</v>
+      </c>
+      <c r="F173" t="s">
+        <v>85</v>
+      </c>
+      <c r="G173" t="s">
+        <v>425</v>
+      </c>
+      <c r="I173" s="3"/>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="C174" t="s">
+        <v>201</v>
+      </c>
+      <c r="D174" t="s">
+        <v>138</v>
+      </c>
+      <c r="E174" t="s">
+        <v>426</v>
+      </c>
+      <c r="F174" t="s">
+        <v>85</v>
+      </c>
+      <c r="G174" t="s">
+        <v>427</v>
+      </c>
+      <c r="I174" s="3"/>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="C175" t="s">
+        <v>201</v>
+      </c>
+      <c r="D175" t="s">
+        <v>53</v>
+      </c>
+      <c r="E175" t="s">
+        <v>428</v>
+      </c>
+      <c r="F175" t="s">
+        <v>85</v>
+      </c>
+      <c r="G175" t="s">
+        <v>429</v>
+      </c>
+      <c r="I175" s="3"/>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="C176" t="s">
+        <v>201</v>
+      </c>
+      <c r="D176" t="s">
+        <v>53</v>
+      </c>
+      <c r="E176" t="s">
+        <v>430</v>
+      </c>
+      <c r="F176" t="s">
+        <v>85</v>
+      </c>
+      <c r="G176" t="s">
+        <v>431</v>
+      </c>
+      <c r="I176" s="3"/>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="C177" t="s">
+        <v>201</v>
+      </c>
+      <c r="D177" t="s">
+        <v>138</v>
+      </c>
+      <c r="E177" t="s">
+        <v>432</v>
+      </c>
+      <c r="F177" t="s">
+        <v>85</v>
+      </c>
+      <c r="G177" t="s">
+        <v>433</v>
+      </c>
+      <c r="I177" s="3"/>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="C178" t="s">
+        <v>201</v>
+      </c>
+      <c r="D178" t="s">
+        <v>53</v>
+      </c>
+      <c r="E178" t="s">
+        <v>434</v>
+      </c>
+      <c r="F178" t="s">
+        <v>85</v>
+      </c>
+      <c r="G178" t="s">
+        <v>435</v>
+      </c>
+      <c r="I178" s="3"/>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="C179" t="s">
+        <v>201</v>
+      </c>
+      <c r="D179" t="s">
+        <v>12</v>
+      </c>
+      <c r="E179" t="s">
+        <v>436</v>
+      </c>
+      <c r="F179" t="s">
+        <v>85</v>
+      </c>
+      <c r="G179" t="s">
+        <v>437</v>
+      </c>
+      <c r="I179" s="3"/>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="C180" t="s">
+        <v>201</v>
+      </c>
+      <c r="D180" t="s">
+        <v>12</v>
+      </c>
+      <c r="E180" t="s">
+        <v>438</v>
+      </c>
+      <c r="F180" t="s">
+        <v>85</v>
+      </c>
+      <c r="G180" t="s">
+        <v>439</v>
+      </c>
+      <c r="I180" s="3"/>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="C181" t="s">
+        <v>201</v>
+      </c>
+      <c r="D181" t="s">
+        <v>12</v>
+      </c>
+      <c r="E181" t="s">
+        <v>440</v>
+      </c>
+      <c r="F181" t="s">
+        <v>85</v>
+      </c>
+      <c r="G181" t="s">
+        <v>441</v>
+      </c>
+      <c r="I181" s="3"/>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="C182" t="s">
+        <v>201</v>
+      </c>
+      <c r="D182" t="s">
+        <v>12</v>
+      </c>
+      <c r="E182" t="s">
+        <v>442</v>
+      </c>
+      <c r="F182" t="s">
+        <v>85</v>
+      </c>
+      <c r="G182" t="s">
+        <v>443</v>
+      </c>
+      <c r="I182" s="3"/>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="C183" t="s">
+        <v>201</v>
+      </c>
+      <c r="D183" t="s">
+        <v>53</v>
+      </c>
+      <c r="E183" t="s">
+        <v>444</v>
+      </c>
+      <c r="F183" t="s">
+        <v>85</v>
+      </c>
+      <c r="G183" t="s">
+        <v>445</v>
+      </c>
+      <c r="I183" s="3"/>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="C184" t="s">
+        <v>201</v>
+      </c>
+      <c r="D184" t="s">
+        <v>12</v>
+      </c>
+      <c r="E184" t="s">
+        <v>446</v>
+      </c>
+      <c r="F184" t="s">
+        <v>85</v>
+      </c>
+      <c r="G184" t="s">
+        <v>447</v>
+      </c>
+      <c r="I184" s="3"/>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="C185" t="s">
+        <v>201</v>
+      </c>
+      <c r="D185" t="s">
+        <v>53</v>
+      </c>
+      <c r="E185" t="s">
+        <v>448</v>
+      </c>
+      <c r="F185" t="s">
+        <v>85</v>
+      </c>
+      <c r="G185" t="s">
+        <v>449</v>
+      </c>
+      <c r="I185" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I2"/>
+  <autoFilter ref="A2:J2"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="H10:H170">
+  <dataValidations count="5">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I10:I95">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="H3:H170">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I100:I185">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I3:I95">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showErrorMessage="1" error="HELD — this starter is not seeded yet. Leave it blank." sqref="I96">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I97:I185">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -5313,7 +5810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -5322,42 +5819,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>418</v>
+        <v>450</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>420</v>
+        <v>452</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>422</v>
+        <v>454</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>424</v>
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>426</v>
+        <v>457</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/pricing/assembly-hours-starter.xlsx
+++ b/pricing/assembly-hours-starter.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="463">
-  <si>
-    <t>STARTER ASSEMBLY HOURS — every starter (183, 1 HELD, 15 NEW since the last version — filter the 'New' column). Your top-30 commercial list first, then the top-30 residential, then the rest. Type YELLOW 'MY HOURS' per assembly (one installed). 'Hours now' is what ships today (blank = not set). Leave blank to keep it. Grey = HELD, leave blank. Send the file back to Track A — do NOT edit hours in the app for this.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="462">
+  <si>
+    <t>STARTER ASSEMBLY HOURS — every starter (183, 15 NEW since the last version — filter the 'New' column). Your top-30 commercial list first, then the top-30 residential, then the rest. Type YELLOW 'MY HOURS' per assembly (one installed). 'Hours now' is what ships today (blank = not set). Leave blank to keep it. Grey = HELD, leave blank. Send the file back to Track A — do NOT edit hours in the app for this.</t>
   </si>
   <si>
     <t>#</t>
@@ -824,9 +824,6 @@
     <t>Surface raceway receptacle (block wall)</t>
   </si>
   <si>
-    <t>HELD - no 700 plate yet. Not seeded until the catalog has: Surface raceway device plate, 700 series. Leave MY HOURS blank.</t>
-  </si>
-  <si>
     <t>NEW</t>
   </si>
   <si>
@@ -1388,7 +1385,7 @@
     <t>HELD</t>
   </si>
   <si>
-    <t>DV34 Surface raceway receptacle (block wall) — grey, and refuses input. It is listed so the sheet is complete, but it is not seeded yet; leave it blank. See its Notes.</t>
+    <t>None.</t>
   </si>
   <si>
     <t>Not in this sheet</t>
@@ -1419,7 +1416,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1429,11 +1426,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1454,15 +1446,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3840,7 +3831,7 @@
       </c>
       <c r="I95" s="3"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>94</v>
       </c>
@@ -3859,32 +3850,29 @@
       <c r="G96" t="s">
         <v>269</v>
       </c>
-      <c r="I96" s="4"/>
-      <c r="J96" s="2" t="s">
-        <v>270</v>
-      </c>
+      <c r="I96" s="3"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C97" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" t="s">
         <v>271</v>
-      </c>
-      <c r="C97" t="s">
-        <v>201</v>
-      </c>
-      <c r="D97" t="s">
-        <v>12</v>
-      </c>
-      <c r="E97" t="s">
-        <v>272</v>
       </c>
       <c r="F97" t="s">
         <v>18</v>
       </c>
       <c r="G97" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I97" s="3"/>
     </row>
@@ -3892,8 +3880,8 @@
       <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98" s="5" t="s">
-        <v>271</v>
+      <c r="B98" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C98" t="s">
         <v>201</v>
@@ -3902,13 +3890,13 @@
         <v>138</v>
       </c>
       <c r="E98" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F98" t="s">
         <v>18</v>
       </c>
       <c r="G98" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I98" s="3"/>
     </row>
@@ -3916,8 +3904,8 @@
       <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99" s="5" t="s">
-        <v>271</v>
+      <c r="B99" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C99" t="s">
         <v>201</v>
@@ -3926,13 +3914,13 @@
         <v>138</v>
       </c>
       <c r="E99" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F99" t="s">
         <v>18</v>
       </c>
       <c r="G99" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I99" s="3"/>
     </row>
@@ -3940,8 +3928,8 @@
       <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100" s="5" t="s">
-        <v>271</v>
+      <c r="B100" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C100" t="s">
         <v>201</v>
@@ -3950,13 +3938,13 @@
         <v>138</v>
       </c>
       <c r="E100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F100" t="s">
         <v>18</v>
       </c>
       <c r="G100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I100" s="3"/>
     </row>
@@ -3971,13 +3959,13 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F101" t="s">
         <v>105</v>
       </c>
       <c r="G101" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I101" s="3"/>
     </row>
@@ -3992,13 +3980,13 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F102" t="s">
         <v>105</v>
       </c>
       <c r="G102" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I102" s="3"/>
     </row>
@@ -4013,13 +4001,13 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F103" t="s">
         <v>105</v>
       </c>
       <c r="G103" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I103" s="3"/>
     </row>
@@ -4034,13 +4022,13 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F104" t="s">
         <v>105</v>
       </c>
       <c r="G104" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I104" s="3"/>
     </row>
@@ -4055,13 +4043,13 @@
         <v>138</v>
       </c>
       <c r="E105" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F105" t="s">
         <v>105</v>
       </c>
       <c r="G105" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I105" s="3"/>
     </row>
@@ -4076,13 +4064,13 @@
         <v>138</v>
       </c>
       <c r="E106" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F106" t="s">
         <v>105</v>
       </c>
       <c r="G106" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I106" s="3"/>
     </row>
@@ -4097,13 +4085,13 @@
         <v>138</v>
       </c>
       <c r="E107" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F107" t="s">
         <v>105</v>
       </c>
       <c r="G107" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I107" s="3"/>
     </row>
@@ -4118,13 +4106,13 @@
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F108" t="s">
         <v>105</v>
       </c>
       <c r="G108" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I108" s="3"/>
     </row>
@@ -4139,13 +4127,13 @@
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F109" t="s">
         <v>105</v>
       </c>
       <c r="G109" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I109" s="3"/>
     </row>
@@ -4160,13 +4148,13 @@
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F110" t="s">
         <v>105</v>
       </c>
       <c r="G110" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I110" s="3"/>
     </row>
@@ -4181,13 +4169,13 @@
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F111" t="s">
         <v>105</v>
       </c>
       <c r="G111" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I111" s="3"/>
     </row>
@@ -4202,13 +4190,13 @@
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F112" t="s">
         <v>105</v>
       </c>
       <c r="G112" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I112" s="3"/>
     </row>
@@ -4223,13 +4211,13 @@
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F113" t="s">
         <v>105</v>
       </c>
       <c r="G113" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I113" s="3"/>
     </row>
@@ -4244,13 +4232,13 @@
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F114" t="s">
         <v>105</v>
       </c>
       <c r="G114" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I114" s="3"/>
     </row>
@@ -4265,13 +4253,13 @@
         <v>138</v>
       </c>
       <c r="E115" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F115" t="s">
         <v>105</v>
       </c>
       <c r="G115" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I115" s="3"/>
     </row>
@@ -4286,13 +4274,13 @@
         <v>53</v>
       </c>
       <c r="E116" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F116" t="s">
         <v>105</v>
       </c>
       <c r="G116" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I116" s="3"/>
     </row>
@@ -4307,13 +4295,13 @@
         <v>138</v>
       </c>
       <c r="E117" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F117" t="s">
         <v>105</v>
       </c>
       <c r="G117" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I117" s="3"/>
     </row>
@@ -4328,13 +4316,13 @@
         <v>138</v>
       </c>
       <c r="E118" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F118" t="s">
         <v>105</v>
       </c>
       <c r="G118" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I118" s="3"/>
     </row>
@@ -4349,13 +4337,13 @@
         <v>138</v>
       </c>
       <c r="E119" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F119" t="s">
         <v>105</v>
       </c>
       <c r="G119" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I119" s="3"/>
     </row>
@@ -4370,13 +4358,13 @@
         <v>138</v>
       </c>
       <c r="E120" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F120" t="s">
         <v>105</v>
       </c>
       <c r="G120" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I120" s="3"/>
     </row>
@@ -4391,13 +4379,13 @@
         <v>138</v>
       </c>
       <c r="E121" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F121" t="s">
         <v>105</v>
       </c>
       <c r="G121" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I121" s="3"/>
     </row>
@@ -4412,13 +4400,13 @@
         <v>138</v>
       </c>
       <c r="E122" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F122" t="s">
         <v>105</v>
       </c>
       <c r="G122" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="I122" s="3"/>
     </row>
@@ -4433,13 +4421,13 @@
         <v>138</v>
       </c>
       <c r="E123" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F123" t="s">
         <v>105</v>
       </c>
       <c r="G123" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I123" s="3"/>
     </row>
@@ -4454,13 +4442,13 @@
         <v>138</v>
       </c>
       <c r="E124" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F124" t="s">
         <v>105</v>
       </c>
       <c r="G124" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I124" s="3"/>
     </row>
@@ -4475,13 +4463,13 @@
         <v>12</v>
       </c>
       <c r="E125" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F125" t="s">
         <v>41</v>
       </c>
       <c r="G125" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I125" s="3"/>
     </row>
@@ -4496,13 +4484,13 @@
         <v>53</v>
       </c>
       <c r="E126" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F126" t="s">
         <v>41</v>
       </c>
       <c r="G126" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I126" s="3"/>
     </row>
@@ -4517,13 +4505,13 @@
         <v>12</v>
       </c>
       <c r="E127" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F127" t="s">
         <v>41</v>
       </c>
       <c r="G127" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I127" s="3"/>
     </row>
@@ -4538,13 +4526,13 @@
         <v>53</v>
       </c>
       <c r="E128" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F128" t="s">
         <v>41</v>
       </c>
       <c r="G128" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I128" s="3"/>
     </row>
@@ -4559,13 +4547,13 @@
         <v>12</v>
       </c>
       <c r="E129" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F129" t="s">
         <v>41</v>
       </c>
       <c r="G129" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I129" s="3"/>
     </row>
@@ -4580,13 +4568,13 @@
         <v>138</v>
       </c>
       <c r="E130" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F130" t="s">
         <v>41</v>
       </c>
       <c r="G130" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I130" s="3"/>
     </row>
@@ -4601,13 +4589,13 @@
         <v>53</v>
       </c>
       <c r="E131" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F131" t="s">
         <v>41</v>
       </c>
       <c r="G131" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I131" s="3"/>
     </row>
@@ -4622,13 +4610,13 @@
         <v>53</v>
       </c>
       <c r="E132" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F132" t="s">
         <v>41</v>
       </c>
       <c r="G132" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I132" s="3"/>
     </row>
@@ -4643,13 +4631,13 @@
         <v>12</v>
       </c>
       <c r="E133" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F133" t="s">
         <v>14</v>
       </c>
       <c r="G133" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I133" s="3"/>
     </row>
@@ -4657,8 +4645,8 @@
       <c r="A134">
         <v>132</v>
       </c>
-      <c r="B134" s="5" t="s">
-        <v>271</v>
+      <c r="B134" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C134" t="s">
         <v>201</v>
@@ -4667,13 +4655,13 @@
         <v>12</v>
       </c>
       <c r="E134" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F134" t="s">
         <v>14</v>
       </c>
       <c r="G134" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I134" s="3"/>
     </row>
@@ -4681,8 +4669,8 @@
       <c r="A135">
         <v>133</v>
       </c>
-      <c r="B135" s="5" t="s">
-        <v>271</v>
+      <c r="B135" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C135" t="s">
         <v>201</v>
@@ -4691,13 +4679,13 @@
         <v>12</v>
       </c>
       <c r="E135" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F135" t="s">
         <v>14</v>
       </c>
       <c r="G135" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I135" s="3"/>
     </row>
@@ -4705,8 +4693,8 @@
       <c r="A136">
         <v>134</v>
       </c>
-      <c r="B136" s="5" t="s">
-        <v>271</v>
+      <c r="B136" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C136" t="s">
         <v>201</v>
@@ -4715,13 +4703,13 @@
         <v>12</v>
       </c>
       <c r="E136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F136" t="s">
         <v>14</v>
       </c>
       <c r="G136" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I136" s="3"/>
     </row>
@@ -4736,13 +4724,13 @@
         <v>138</v>
       </c>
       <c r="E137" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F137" t="s">
         <v>14</v>
       </c>
       <c r="G137" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I137" s="3"/>
     </row>
@@ -4757,13 +4745,13 @@
         <v>53</v>
       </c>
       <c r="E138" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F138" t="s">
         <v>14</v>
       </c>
       <c r="G138" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I138" s="3"/>
     </row>
@@ -4778,13 +4766,13 @@
         <v>53</v>
       </c>
       <c r="E139" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F139" t="s">
         <v>14</v>
       </c>
       <c r="G139" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I139" s="3"/>
     </row>
@@ -4799,13 +4787,13 @@
         <v>53</v>
       </c>
       <c r="E140" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F140" t="s">
         <v>14</v>
       </c>
       <c r="G140" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I140" s="3"/>
     </row>
@@ -4820,13 +4808,13 @@
         <v>138</v>
       </c>
       <c r="E141" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F141" t="s">
         <v>14</v>
       </c>
       <c r="G141" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I141" s="3"/>
     </row>
@@ -4841,13 +4829,13 @@
         <v>138</v>
       </c>
       <c r="E142" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F142" t="s">
         <v>14</v>
       </c>
       <c r="G142" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I142" s="3"/>
     </row>
@@ -4862,13 +4850,13 @@
         <v>138</v>
       </c>
       <c r="E143" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F143" t="s">
         <v>14</v>
       </c>
       <c r="G143" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I143" s="3"/>
     </row>
@@ -4883,13 +4871,13 @@
         <v>138</v>
       </c>
       <c r="E144" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F144" t="s">
         <v>14</v>
       </c>
       <c r="G144" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I144" s="3"/>
     </row>
@@ -4904,13 +4892,13 @@
         <v>53</v>
       </c>
       <c r="E145" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F145" t="s">
         <v>14</v>
       </c>
       <c r="G145" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I145" s="3"/>
     </row>
@@ -4925,13 +4913,13 @@
         <v>138</v>
       </c>
       <c r="E146" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F146" t="s">
         <v>14</v>
       </c>
       <c r="G146" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I146" s="3"/>
     </row>
@@ -4946,13 +4934,13 @@
         <v>138</v>
       </c>
       <c r="E147" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F147" t="s">
         <v>14</v>
       </c>
       <c r="G147" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I147" s="3"/>
     </row>
@@ -4967,13 +4955,13 @@
         <v>12</v>
       </c>
       <c r="E148" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F148" t="s">
         <v>14</v>
       </c>
       <c r="G148" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I148" s="3"/>
     </row>
@@ -4988,13 +4976,13 @@
         <v>12</v>
       </c>
       <c r="E149" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F149" t="s">
         <v>14</v>
       </c>
       <c r="G149" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I149" s="3"/>
     </row>
@@ -5009,13 +4997,13 @@
         <v>12</v>
       </c>
       <c r="E150" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F150" t="s">
         <v>14</v>
       </c>
       <c r="G150" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I150" s="3"/>
     </row>
@@ -5030,13 +5018,13 @@
         <v>12</v>
       </c>
       <c r="E151" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F151" t="s">
         <v>14</v>
       </c>
       <c r="G151" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I151" s="3"/>
     </row>
@@ -5051,13 +5039,13 @@
         <v>12</v>
       </c>
       <c r="E152" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F152" t="s">
         <v>14</v>
       </c>
       <c r="G152" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I152" s="3"/>
     </row>
@@ -5065,8 +5053,8 @@
       <c r="A153">
         <v>151</v>
       </c>
-      <c r="B153" s="5" t="s">
-        <v>271</v>
+      <c r="B153" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C153" t="s">
         <v>201</v>
@@ -5075,13 +5063,13 @@
         <v>53</v>
       </c>
       <c r="E153" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F153" t="s">
         <v>14</v>
       </c>
       <c r="G153" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I153" s="3"/>
     </row>
@@ -5089,8 +5077,8 @@
       <c r="A154">
         <v>152</v>
       </c>
-      <c r="B154" s="5" t="s">
-        <v>271</v>
+      <c r="B154" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C154" t="s">
         <v>201</v>
@@ -5099,13 +5087,13 @@
         <v>53</v>
       </c>
       <c r="E154" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F154" t="s">
         <v>14</v>
       </c>
       <c r="G154" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I154" s="3"/>
     </row>
@@ -5113,8 +5101,8 @@
       <c r="A155">
         <v>153</v>
       </c>
-      <c r="B155" s="5" t="s">
-        <v>271</v>
+      <c r="B155" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C155" t="s">
         <v>201</v>
@@ -5123,13 +5111,13 @@
         <v>53</v>
       </c>
       <c r="E155" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F155" t="s">
         <v>14</v>
       </c>
       <c r="G155" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I155" s="3"/>
     </row>
@@ -5144,13 +5132,13 @@
         <v>12</v>
       </c>
       <c r="E156" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F156" t="s">
         <v>89</v>
       </c>
       <c r="G156" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I156" s="3"/>
     </row>
@@ -5165,13 +5153,13 @@
         <v>12</v>
       </c>
       <c r="E157" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F157" t="s">
         <v>89</v>
       </c>
       <c r="G157" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I157" s="3"/>
     </row>
@@ -5186,13 +5174,13 @@
         <v>12</v>
       </c>
       <c r="E158" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F158" t="s">
         <v>89</v>
       </c>
       <c r="G158" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I158" s="3"/>
     </row>
@@ -5207,13 +5195,13 @@
         <v>12</v>
       </c>
       <c r="E159" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F159" t="s">
         <v>89</v>
       </c>
       <c r="G159" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I159" s="3"/>
     </row>
@@ -5228,13 +5216,13 @@
         <v>138</v>
       </c>
       <c r="E160" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F160" t="s">
         <v>89</v>
       </c>
       <c r="G160" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I160" s="3"/>
     </row>
@@ -5249,13 +5237,13 @@
         <v>138</v>
       </c>
       <c r="E161" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F161" t="s">
         <v>89</v>
       </c>
       <c r="G161" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I161" s="3"/>
     </row>
@@ -5270,13 +5258,13 @@
         <v>53</v>
       </c>
       <c r="E162" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F162" t="s">
         <v>89</v>
       </c>
       <c r="G162" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I162" s="3"/>
     </row>
@@ -5291,13 +5279,13 @@
         <v>138</v>
       </c>
       <c r="E163" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F163" t="s">
         <v>89</v>
       </c>
       <c r="G163" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I163" s="3"/>
     </row>
@@ -5312,13 +5300,13 @@
         <v>12</v>
       </c>
       <c r="E164" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F164" t="s">
         <v>89</v>
       </c>
       <c r="G164" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I164" s="3"/>
     </row>
@@ -5333,13 +5321,13 @@
         <v>138</v>
       </c>
       <c r="E165" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F165" t="s">
         <v>89</v>
       </c>
       <c r="G165" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I165" s="3"/>
     </row>
@@ -5354,13 +5342,13 @@
         <v>138</v>
       </c>
       <c r="E166" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F166" t="s">
         <v>89</v>
       </c>
       <c r="G166" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I166" s="3"/>
     </row>
@@ -5368,8 +5356,8 @@
       <c r="A167">
         <v>165</v>
       </c>
-      <c r="B167" s="5" t="s">
-        <v>271</v>
+      <c r="B167" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C167" t="s">
         <v>201</v>
@@ -5378,13 +5366,13 @@
         <v>12</v>
       </c>
       <c r="E167" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F167" t="s">
         <v>85</v>
       </c>
       <c r="G167" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I167" s="3"/>
     </row>
@@ -5392,8 +5380,8 @@
       <c r="A168">
         <v>166</v>
       </c>
-      <c r="B168" s="5" t="s">
-        <v>271</v>
+      <c r="B168" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C168" t="s">
         <v>201</v>
@@ -5402,13 +5390,13 @@
         <v>138</v>
       </c>
       <c r="E168" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F168" t="s">
         <v>85</v>
       </c>
       <c r="G168" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I168" s="3"/>
     </row>
@@ -5416,8 +5404,8 @@
       <c r="A169">
         <v>167</v>
       </c>
-      <c r="B169" s="5" t="s">
-        <v>271</v>
+      <c r="B169" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C169" t="s">
         <v>201</v>
@@ -5426,13 +5414,13 @@
         <v>138</v>
       </c>
       <c r="E169" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F169" t="s">
         <v>85</v>
       </c>
       <c r="G169" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I169" s="3"/>
     </row>
@@ -5440,8 +5428,8 @@
       <c r="A170">
         <v>168</v>
       </c>
-      <c r="B170" s="5" t="s">
-        <v>271</v>
+      <c r="B170" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C170" t="s">
         <v>201</v>
@@ -5450,13 +5438,13 @@
         <v>138</v>
       </c>
       <c r="E170" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F170" t="s">
         <v>85</v>
       </c>
       <c r="G170" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I170" s="3"/>
     </row>
@@ -5464,8 +5452,8 @@
       <c r="A171">
         <v>169</v>
       </c>
-      <c r="B171" s="5" t="s">
-        <v>271</v>
+      <c r="B171" s="4" t="s">
+        <v>270</v>
       </c>
       <c r="C171" t="s">
         <v>201</v>
@@ -5474,13 +5462,13 @@
         <v>138</v>
       </c>
       <c r="E171" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F171" t="s">
         <v>85</v>
       </c>
       <c r="G171" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I171" s="3"/>
     </row>
@@ -5495,13 +5483,13 @@
         <v>53</v>
       </c>
       <c r="E172" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F172" t="s">
         <v>85</v>
       </c>
       <c r="G172" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H172">
         <v>8</v>
@@ -5519,13 +5507,13 @@
         <v>53</v>
       </c>
       <c r="E173" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F173" t="s">
         <v>85</v>
       </c>
       <c r="G173" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I173" s="3"/>
     </row>
@@ -5540,13 +5528,13 @@
         <v>138</v>
       </c>
       <c r="E174" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F174" t="s">
         <v>85</v>
       </c>
       <c r="G174" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I174" s="3"/>
     </row>
@@ -5561,13 +5549,13 @@
         <v>53</v>
       </c>
       <c r="E175" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F175" t="s">
         <v>85</v>
       </c>
       <c r="G175" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="I175" s="3"/>
     </row>
@@ -5582,13 +5570,13 @@
         <v>53</v>
       </c>
       <c r="E176" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F176" t="s">
         <v>85</v>
       </c>
       <c r="G176" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="I176" s="3"/>
     </row>
@@ -5603,13 +5591,13 @@
         <v>138</v>
       </c>
       <c r="E177" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F177" t="s">
         <v>85</v>
       </c>
       <c r="G177" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I177" s="3"/>
     </row>
@@ -5624,13 +5612,13 @@
         <v>53</v>
       </c>
       <c r="E178" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F178" t="s">
         <v>85</v>
       </c>
       <c r="G178" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I178" s="3"/>
     </row>
@@ -5645,13 +5633,13 @@
         <v>12</v>
       </c>
       <c r="E179" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F179" t="s">
         <v>85</v>
       </c>
       <c r="G179" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="I179" s="3"/>
     </row>
@@ -5666,13 +5654,13 @@
         <v>12</v>
       </c>
       <c r="E180" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F180" t="s">
         <v>85</v>
       </c>
       <c r="G180" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I180" s="3"/>
     </row>
@@ -5687,13 +5675,13 @@
         <v>12</v>
       </c>
       <c r="E181" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F181" t="s">
         <v>85</v>
       </c>
       <c r="G181" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I181" s="3"/>
     </row>
@@ -5708,13 +5696,13 @@
         <v>12</v>
       </c>
       <c r="E182" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F182" t="s">
         <v>85</v>
       </c>
       <c r="G182" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I182" s="3"/>
     </row>
@@ -5729,13 +5717,13 @@
         <v>53</v>
       </c>
       <c r="E183" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F183" t="s">
         <v>85</v>
       </c>
       <c r="G183" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="I183" s="3"/>
     </row>
@@ -5750,13 +5738,13 @@
         <v>12</v>
       </c>
       <c r="E184" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F184" t="s">
         <v>85</v>
       </c>
       <c r="G184" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I184" s="3"/>
     </row>
@@ -5771,13 +5759,13 @@
         <v>53</v>
       </c>
       <c r="E185" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F185" t="s">
         <v>85</v>
       </c>
       <c r="G185" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="I185" s="3"/>
     </row>
@@ -5786,20 +5774,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I10:I95">
+  <dataValidations count="2">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I10:I185">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I100:I185">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I3:I95">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="textLength" operator="equal" allowBlank="1" showErrorMessage="1" error="HELD — this starter is not seeded yet. Leave it blank." sqref="I96">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I97:I185">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I3:I185">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -5819,58 +5798,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>450</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>452</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>454</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>456</v>
+      <c r="B4" s="5" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>459</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>461</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/pricing/assembly-hours-starter.xlsx
+++ b/pricing/assembly-hours-starter.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="462">
-  <si>
-    <t>STARTER ASSEMBLY HOURS — every starter (183, 15 NEW since the last version — filter the 'New' column). Your top-30 commercial list first, then the top-30 residential, then the rest. Type YELLOW 'MY HOURS' per assembly (one installed). 'Hours now' is what ships today (blank = not set). Leave blank to keep it. Grey = HELD, leave blank. Send the file back to Track A — do NOT edit hours in the app for this.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="461">
+  <si>
+    <t>STARTER ASSEMBLY HOURS — every starter (183, 0 NEW since the last version — filter the 'New' column). Your top-30 commercial list first, then the top-30 residential, then the rest. Type YELLOW 'MY HOURS' per assembly (one installed). 'Hours now' is what ships today (blank = not set). Leave blank to keep it. Grey = HELD, leave blank. Send the file back to Track A — do NOT edit hours in the app for this.</t>
   </si>
   <si>
     <t>#</t>
@@ -824,9 +824,6 @@
     <t>Surface raceway receptacle (block wall)</t>
   </si>
   <si>
-    <t>NEW</t>
-  </si>
-  <si>
     <t>GC5</t>
   </si>
   <si>
@@ -1379,7 +1376,7 @@
     <t>Your top-30 commercial list, then the top-30 residential list (references/top-assemblies-draft.md), then every other starter by category.</t>
   </si>
   <si>
-    <t>15 rows say NEW: starters added since the version this was compared with (ah-previous.xlsx). Filter the 'New' column to see only them.</t>
+    <t>0 rows say NEW: starters added since the version this was compared with (assembly-hours-prev.xlsx). Filter the 'New' column to see only them.</t>
   </si>
   <si>
     <t>HELD</t>
@@ -1416,7 +1413,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1426,11 +1423,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -1446,14 +1438,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3856,23 +3847,20 @@
       <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="C97" t="s">
+        <v>201</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" t="s">
         <v>270</v>
-      </c>
-      <c r="C97" t="s">
-        <v>201</v>
-      </c>
-      <c r="D97" t="s">
-        <v>12</v>
-      </c>
-      <c r="E97" t="s">
-        <v>271</v>
       </c>
       <c r="F97" t="s">
         <v>18</v>
       </c>
       <c r="G97" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I97" s="3"/>
     </row>
@@ -3880,9 +3868,6 @@
       <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C98" t="s">
         <v>201</v>
       </c>
@@ -3890,13 +3875,13 @@
         <v>138</v>
       </c>
       <c r="E98" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F98" t="s">
         <v>18</v>
       </c>
       <c r="G98" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I98" s="3"/>
     </row>
@@ -3904,9 +3889,6 @@
       <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C99" t="s">
         <v>201</v>
       </c>
@@ -3914,13 +3896,13 @@
         <v>138</v>
       </c>
       <c r="E99" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F99" t="s">
         <v>18</v>
       </c>
       <c r="G99" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I99" s="3"/>
     </row>
@@ -3928,9 +3910,6 @@
       <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C100" t="s">
         <v>201</v>
       </c>
@@ -3938,13 +3917,13 @@
         <v>138</v>
       </c>
       <c r="E100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F100" t="s">
         <v>18</v>
       </c>
       <c r="G100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I100" s="3"/>
     </row>
@@ -3959,13 +3938,13 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F101" t="s">
         <v>105</v>
       </c>
       <c r="G101" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I101" s="3"/>
     </row>
@@ -3980,13 +3959,13 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F102" t="s">
         <v>105</v>
       </c>
       <c r="G102" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I102" s="3"/>
     </row>
@@ -4001,13 +3980,13 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F103" t="s">
         <v>105</v>
       </c>
       <c r="G103" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I103" s="3"/>
     </row>
@@ -4022,13 +4001,13 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F104" t="s">
         <v>105</v>
       </c>
       <c r="G104" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I104" s="3"/>
     </row>
@@ -4043,13 +4022,13 @@
         <v>138</v>
       </c>
       <c r="E105" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F105" t="s">
         <v>105</v>
       </c>
       <c r="G105" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I105" s="3"/>
     </row>
@@ -4064,13 +4043,13 @@
         <v>138</v>
       </c>
       <c r="E106" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F106" t="s">
         <v>105</v>
       </c>
       <c r="G106" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I106" s="3"/>
     </row>
@@ -4085,13 +4064,13 @@
         <v>138</v>
       </c>
       <c r="E107" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F107" t="s">
         <v>105</v>
       </c>
       <c r="G107" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I107" s="3"/>
     </row>
@@ -4106,13 +4085,13 @@
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F108" t="s">
         <v>105</v>
       </c>
       <c r="G108" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I108" s="3"/>
     </row>
@@ -4127,13 +4106,13 @@
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F109" t="s">
         <v>105</v>
       </c>
       <c r="G109" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I109" s="3"/>
     </row>
@@ -4148,13 +4127,13 @@
         <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F110" t="s">
         <v>105</v>
       </c>
       <c r="G110" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I110" s="3"/>
     </row>
@@ -4169,13 +4148,13 @@
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F111" t="s">
         <v>105</v>
       </c>
       <c r="G111" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I111" s="3"/>
     </row>
@@ -4190,13 +4169,13 @@
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F112" t="s">
         <v>105</v>
       </c>
       <c r="G112" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="I112" s="3"/>
     </row>
@@ -4211,13 +4190,13 @@
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F113" t="s">
         <v>105</v>
       </c>
       <c r="G113" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="I113" s="3"/>
     </row>
@@ -4232,13 +4211,13 @@
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F114" t="s">
         <v>105</v>
       </c>
       <c r="G114" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I114" s="3"/>
     </row>
@@ -4253,13 +4232,13 @@
         <v>138</v>
       </c>
       <c r="E115" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F115" t="s">
         <v>105</v>
       </c>
       <c r="G115" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="I115" s="3"/>
     </row>
@@ -4274,13 +4253,13 @@
         <v>53</v>
       </c>
       <c r="E116" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F116" t="s">
         <v>105</v>
       </c>
       <c r="G116" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I116" s="3"/>
     </row>
@@ -4295,13 +4274,13 @@
         <v>138</v>
       </c>
       <c r="E117" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F117" t="s">
         <v>105</v>
       </c>
       <c r="G117" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I117" s="3"/>
     </row>
@@ -4316,13 +4295,13 @@
         <v>138</v>
       </c>
       <c r="E118" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F118" t="s">
         <v>105</v>
       </c>
       <c r="G118" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I118" s="3"/>
     </row>
@@ -4337,13 +4316,13 @@
         <v>138</v>
       </c>
       <c r="E119" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F119" t="s">
         <v>105</v>
       </c>
       <c r="G119" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="I119" s="3"/>
     </row>
@@ -4358,13 +4337,13 @@
         <v>138</v>
       </c>
       <c r="E120" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F120" t="s">
         <v>105</v>
       </c>
       <c r="G120" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I120" s="3"/>
     </row>
@@ -4379,13 +4358,13 @@
         <v>138</v>
       </c>
       <c r="E121" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F121" t="s">
         <v>105</v>
       </c>
       <c r="G121" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I121" s="3"/>
     </row>
@@ -4400,13 +4379,13 @@
         <v>138</v>
       </c>
       <c r="E122" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F122" t="s">
         <v>105</v>
       </c>
       <c r="G122" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I122" s="3"/>
     </row>
@@ -4421,13 +4400,13 @@
         <v>138</v>
       </c>
       <c r="E123" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F123" t="s">
         <v>105</v>
       </c>
       <c r="G123" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I123" s="3"/>
     </row>
@@ -4442,13 +4421,13 @@
         <v>138</v>
       </c>
       <c r="E124" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F124" t="s">
         <v>105</v>
       </c>
       <c r="G124" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I124" s="3"/>
     </row>
@@ -4463,13 +4442,13 @@
         <v>12</v>
       </c>
       <c r="E125" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F125" t="s">
         <v>41</v>
       </c>
       <c r="G125" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I125" s="3"/>
     </row>
@@ -4484,13 +4463,13 @@
         <v>53</v>
       </c>
       <c r="E126" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F126" t="s">
         <v>41</v>
       </c>
       <c r="G126" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I126" s="3"/>
     </row>
@@ -4505,13 +4484,13 @@
         <v>12</v>
       </c>
       <c r="E127" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F127" t="s">
         <v>41</v>
       </c>
       <c r="G127" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I127" s="3"/>
     </row>
@@ -4526,13 +4505,13 @@
         <v>53</v>
       </c>
       <c r="E128" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F128" t="s">
         <v>41</v>
       </c>
       <c r="G128" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I128" s="3"/>
     </row>
@@ -4547,13 +4526,13 @@
         <v>12</v>
       </c>
       <c r="E129" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F129" t="s">
         <v>41</v>
       </c>
       <c r="G129" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I129" s="3"/>
     </row>
@@ -4568,13 +4547,13 @@
         <v>138</v>
       </c>
       <c r="E130" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F130" t="s">
         <v>41</v>
       </c>
       <c r="G130" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I130" s="3"/>
     </row>
@@ -4589,13 +4568,13 @@
         <v>53</v>
       </c>
       <c r="E131" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F131" t="s">
         <v>41</v>
       </c>
       <c r="G131" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I131" s="3"/>
     </row>
@@ -4610,13 +4589,13 @@
         <v>53</v>
       </c>
       <c r="E132" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F132" t="s">
         <v>41</v>
       </c>
       <c r="G132" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I132" s="3"/>
     </row>
@@ -4631,13 +4610,13 @@
         <v>12</v>
       </c>
       <c r="E133" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F133" t="s">
         <v>14</v>
       </c>
       <c r="G133" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I133" s="3"/>
     </row>
@@ -4645,9 +4624,6 @@
       <c r="A134">
         <v>132</v>
       </c>
-      <c r="B134" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C134" t="s">
         <v>201</v>
       </c>
@@ -4655,13 +4631,13 @@
         <v>12</v>
       </c>
       <c r="E134" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F134" t="s">
         <v>14</v>
       </c>
       <c r="G134" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I134" s="3"/>
     </row>
@@ -4669,9 +4645,6 @@
       <c r="A135">
         <v>133</v>
       </c>
-      <c r="B135" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C135" t="s">
         <v>201</v>
       </c>
@@ -4679,13 +4652,13 @@
         <v>12</v>
       </c>
       <c r="E135" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F135" t="s">
         <v>14</v>
       </c>
       <c r="G135" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I135" s="3"/>
     </row>
@@ -4693,9 +4666,6 @@
       <c r="A136">
         <v>134</v>
       </c>
-      <c r="B136" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C136" t="s">
         <v>201</v>
       </c>
@@ -4703,13 +4673,13 @@
         <v>12</v>
       </c>
       <c r="E136" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F136" t="s">
         <v>14</v>
       </c>
       <c r="G136" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I136" s="3"/>
     </row>
@@ -4724,13 +4694,13 @@
         <v>138</v>
       </c>
       <c r="E137" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F137" t="s">
         <v>14</v>
       </c>
       <c r="G137" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I137" s="3"/>
     </row>
@@ -4745,13 +4715,13 @@
         <v>53</v>
       </c>
       <c r="E138" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F138" t="s">
         <v>14</v>
       </c>
       <c r="G138" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I138" s="3"/>
     </row>
@@ -4766,13 +4736,13 @@
         <v>53</v>
       </c>
       <c r="E139" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F139" t="s">
         <v>14</v>
       </c>
       <c r="G139" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I139" s="3"/>
     </row>
@@ -4787,13 +4757,13 @@
         <v>53</v>
       </c>
       <c r="E140" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F140" t="s">
         <v>14</v>
       </c>
       <c r="G140" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I140" s="3"/>
     </row>
@@ -4808,13 +4778,13 @@
         <v>138</v>
       </c>
       <c r="E141" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F141" t="s">
         <v>14</v>
       </c>
       <c r="G141" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I141" s="3"/>
     </row>
@@ -4829,13 +4799,13 @@
         <v>138</v>
       </c>
       <c r="E142" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F142" t="s">
         <v>14</v>
       </c>
       <c r="G142" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I142" s="3"/>
     </row>
@@ -4850,13 +4820,13 @@
         <v>138</v>
       </c>
       <c r="E143" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F143" t="s">
         <v>14</v>
       </c>
       <c r="G143" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I143" s="3"/>
     </row>
@@ -4871,13 +4841,13 @@
         <v>138</v>
       </c>
       <c r="E144" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F144" t="s">
         <v>14</v>
       </c>
       <c r="G144" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I144" s="3"/>
     </row>
@@ -4892,13 +4862,13 @@
         <v>53</v>
       </c>
       <c r="E145" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F145" t="s">
         <v>14</v>
       </c>
       <c r="G145" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I145" s="3"/>
     </row>
@@ -4913,13 +4883,13 @@
         <v>138</v>
       </c>
       <c r="E146" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F146" t="s">
         <v>14</v>
       </c>
       <c r="G146" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I146" s="3"/>
     </row>
@@ -4934,13 +4904,13 @@
         <v>138</v>
       </c>
       <c r="E147" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F147" t="s">
         <v>14</v>
       </c>
       <c r="G147" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I147" s="3"/>
     </row>
@@ -4955,13 +4925,13 @@
         <v>12</v>
       </c>
       <c r="E148" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F148" t="s">
         <v>14</v>
       </c>
       <c r="G148" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I148" s="3"/>
     </row>
@@ -4976,13 +4946,13 @@
         <v>12</v>
       </c>
       <c r="E149" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F149" t="s">
         <v>14</v>
       </c>
       <c r="G149" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I149" s="3"/>
     </row>
@@ -4997,13 +4967,13 @@
         <v>12</v>
       </c>
       <c r="E150" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F150" t="s">
         <v>14</v>
       </c>
       <c r="G150" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I150" s="3"/>
     </row>
@@ -5018,13 +4988,13 @@
         <v>12</v>
       </c>
       <c r="E151" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F151" t="s">
         <v>14</v>
       </c>
       <c r="G151" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I151" s="3"/>
     </row>
@@ -5039,13 +5009,13 @@
         <v>12</v>
       </c>
       <c r="E152" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F152" t="s">
         <v>14</v>
       </c>
       <c r="G152" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I152" s="3"/>
     </row>
@@ -5053,9 +5023,6 @@
       <c r="A153">
         <v>151</v>
       </c>
-      <c r="B153" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C153" t="s">
         <v>201</v>
       </c>
@@ -5063,13 +5030,13 @@
         <v>53</v>
       </c>
       <c r="E153" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F153" t="s">
         <v>14</v>
       </c>
       <c r="G153" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I153" s="3"/>
     </row>
@@ -5077,9 +5044,6 @@
       <c r="A154">
         <v>152</v>
       </c>
-      <c r="B154" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C154" t="s">
         <v>201</v>
       </c>
@@ -5087,13 +5051,13 @@
         <v>53</v>
       </c>
       <c r="E154" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F154" t="s">
         <v>14</v>
       </c>
       <c r="G154" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I154" s="3"/>
     </row>
@@ -5101,9 +5065,6 @@
       <c r="A155">
         <v>153</v>
       </c>
-      <c r="B155" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C155" t="s">
         <v>201</v>
       </c>
@@ -5111,13 +5072,13 @@
         <v>53</v>
       </c>
       <c r="E155" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F155" t="s">
         <v>14</v>
       </c>
       <c r="G155" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I155" s="3"/>
     </row>
@@ -5132,13 +5093,13 @@
         <v>12</v>
       </c>
       <c r="E156" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F156" t="s">
         <v>89</v>
       </c>
       <c r="G156" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I156" s="3"/>
     </row>
@@ -5153,13 +5114,13 @@
         <v>12</v>
       </c>
       <c r="E157" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F157" t="s">
         <v>89</v>
       </c>
       <c r="G157" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I157" s="3"/>
     </row>
@@ -5174,13 +5135,13 @@
         <v>12</v>
       </c>
       <c r="E158" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F158" t="s">
         <v>89</v>
       </c>
       <c r="G158" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I158" s="3"/>
     </row>
@@ -5195,13 +5156,13 @@
         <v>12</v>
       </c>
       <c r="E159" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F159" t="s">
         <v>89</v>
       </c>
       <c r="G159" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I159" s="3"/>
     </row>
@@ -5216,13 +5177,13 @@
         <v>138</v>
       </c>
       <c r="E160" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F160" t="s">
         <v>89</v>
       </c>
       <c r="G160" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I160" s="3"/>
     </row>
@@ -5237,13 +5198,13 @@
         <v>138</v>
       </c>
       <c r="E161" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F161" t="s">
         <v>89</v>
       </c>
       <c r="G161" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I161" s="3"/>
     </row>
@@ -5258,13 +5219,13 @@
         <v>53</v>
       </c>
       <c r="E162" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F162" t="s">
         <v>89</v>
       </c>
       <c r="G162" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I162" s="3"/>
     </row>
@@ -5279,13 +5240,13 @@
         <v>138</v>
       </c>
       <c r="E163" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F163" t="s">
         <v>89</v>
       </c>
       <c r="G163" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I163" s="3"/>
     </row>
@@ -5300,13 +5261,13 @@
         <v>12</v>
       </c>
       <c r="E164" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F164" t="s">
         <v>89</v>
       </c>
       <c r="G164" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I164" s="3"/>
     </row>
@@ -5321,13 +5282,13 @@
         <v>138</v>
       </c>
       <c r="E165" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F165" t="s">
         <v>89</v>
       </c>
       <c r="G165" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I165" s="3"/>
     </row>
@@ -5342,13 +5303,13 @@
         <v>138</v>
       </c>
       <c r="E166" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F166" t="s">
         <v>89</v>
       </c>
       <c r="G166" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I166" s="3"/>
     </row>
@@ -5356,9 +5317,6 @@
       <c r="A167">
         <v>165</v>
       </c>
-      <c r="B167" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C167" t="s">
         <v>201</v>
       </c>
@@ -5366,13 +5324,13 @@
         <v>12</v>
       </c>
       <c r="E167" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F167" t="s">
         <v>85</v>
       </c>
       <c r="G167" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I167" s="3"/>
     </row>
@@ -5380,9 +5338,6 @@
       <c r="A168">
         <v>166</v>
       </c>
-      <c r="B168" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C168" t="s">
         <v>201</v>
       </c>
@@ -5390,13 +5345,13 @@
         <v>138</v>
       </c>
       <c r="E168" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F168" t="s">
         <v>85</v>
       </c>
       <c r="G168" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I168" s="3"/>
     </row>
@@ -5404,9 +5359,6 @@
       <c r="A169">
         <v>167</v>
       </c>
-      <c r="B169" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C169" t="s">
         <v>201</v>
       </c>
@@ -5414,13 +5366,13 @@
         <v>138</v>
       </c>
       <c r="E169" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F169" t="s">
         <v>85</v>
       </c>
       <c r="G169" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I169" s="3"/>
     </row>
@@ -5428,9 +5380,6 @@
       <c r="A170">
         <v>168</v>
       </c>
-      <c r="B170" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C170" t="s">
         <v>201</v>
       </c>
@@ -5438,13 +5387,13 @@
         <v>138</v>
       </c>
       <c r="E170" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F170" t="s">
         <v>85</v>
       </c>
       <c r="G170" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I170" s="3"/>
     </row>
@@ -5452,9 +5401,6 @@
       <c r="A171">
         <v>169</v>
       </c>
-      <c r="B171" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="C171" t="s">
         <v>201</v>
       </c>
@@ -5462,13 +5408,13 @@
         <v>138</v>
       </c>
       <c r="E171" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F171" t="s">
         <v>85</v>
       </c>
       <c r="G171" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I171" s="3"/>
     </row>
@@ -5483,13 +5429,13 @@
         <v>53</v>
       </c>
       <c r="E172" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F172" t="s">
         <v>85</v>
       </c>
       <c r="G172" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H172">
         <v>8</v>
@@ -5507,13 +5453,13 @@
         <v>53</v>
       </c>
       <c r="E173" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F173" t="s">
         <v>85</v>
       </c>
       <c r="G173" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I173" s="3"/>
     </row>
@@ -5528,13 +5474,13 @@
         <v>138</v>
       </c>
       <c r="E174" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F174" t="s">
         <v>85</v>
       </c>
       <c r="G174" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I174" s="3"/>
     </row>
@@ -5549,13 +5495,13 @@
         <v>53</v>
       </c>
       <c r="E175" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F175" t="s">
         <v>85</v>
       </c>
       <c r="G175" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I175" s="3"/>
     </row>
@@ -5570,13 +5516,13 @@
         <v>53</v>
       </c>
       <c r="E176" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F176" t="s">
         <v>85</v>
       </c>
       <c r="G176" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="I176" s="3"/>
     </row>
@@ -5591,13 +5537,13 @@
         <v>138</v>
       </c>
       <c r="E177" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F177" t="s">
         <v>85</v>
       </c>
       <c r="G177" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I177" s="3"/>
     </row>
@@ -5612,13 +5558,13 @@
         <v>53</v>
       </c>
       <c r="E178" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F178" t="s">
         <v>85</v>
       </c>
       <c r="G178" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I178" s="3"/>
     </row>
@@ -5633,13 +5579,13 @@
         <v>12</v>
       </c>
       <c r="E179" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F179" t="s">
         <v>85</v>
       </c>
       <c r="G179" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I179" s="3"/>
     </row>
@@ -5654,13 +5600,13 @@
         <v>12</v>
       </c>
       <c r="E180" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F180" t="s">
         <v>85</v>
       </c>
       <c r="G180" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="I180" s="3"/>
     </row>
@@ -5675,13 +5621,13 @@
         <v>12</v>
       </c>
       <c r="E181" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F181" t="s">
         <v>85</v>
       </c>
       <c r="G181" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I181" s="3"/>
     </row>
@@ -5696,13 +5642,13 @@
         <v>12</v>
       </c>
       <c r="E182" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F182" t="s">
         <v>85</v>
       </c>
       <c r="G182" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="I182" s="3"/>
     </row>
@@ -5717,13 +5663,13 @@
         <v>53</v>
       </c>
       <c r="E183" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F183" t="s">
         <v>85</v>
       </c>
       <c r="G183" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I183" s="3"/>
     </row>
@@ -5738,13 +5684,13 @@
         <v>12</v>
       </c>
       <c r="E184" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F184" t="s">
         <v>85</v>
       </c>
       <c r="G184" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I184" s="3"/>
     </row>
@@ -5759,13 +5705,13 @@
         <v>53</v>
       </c>
       <c r="E185" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F185" t="s">
         <v>85</v>
       </c>
       <c r="G185" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="I185" s="3"/>
     </row>
@@ -5798,58 +5744,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>451</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>455</v>
+      <c r="B4" s="4" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>461</v>
       </c>
     </row>
   </sheetData>

--- a/pricing/assembly-hours-starter.xlsx
+++ b/pricing/assembly-hours-starter.xlsx
@@ -12,9 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="461">
-  <si>
-    <t>STARTER ASSEMBLY HOURS — every starter (183, 0 NEW since the last version — filter the 'New' column). Your top-30 commercial list first, then the top-30 residential, then the rest. Type YELLOW 'MY HOURS' per assembly (one installed). 'Hours now' is what ships today (blank = not set). Leave blank to keep it. Grey = HELD, leave blank. Send the file back to Track A — do NOT edit hours in the app for this.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="543">
+  <si>
+    <t>STARTER ASSEMBLY HOURS — every starter (224). Your top-30 commercial list first, then the top-30 residential, then the rest. Type YELLOW 'MY HOURS' per assembly (one installed). 'Hours now' is what ships today (blank = not set). Leave blank to keep it. Grey = HELD, leave blank. Send the file back to Track A — do NOT edit hours in the app for this.</t>
   </si>
   <si>
     <t>#</t>
@@ -686,6 +686,60 @@
     <t>Recessed can LED retrofit (resi)</t>
   </si>
   <si>
+    <t>CK6</t>
+  </si>
+  <si>
+    <t>208V cooler / freezer receptacle (NEMA 6-20)</t>
+  </si>
+  <si>
+    <t>CK7</t>
+  </si>
+  <si>
+    <t>Duplex receptacle, EMT</t>
+  </si>
+  <si>
+    <t>CK8</t>
+  </si>
+  <si>
+    <t>Two switches, one box, MC</t>
+  </si>
+  <si>
+    <t>CK10</t>
+  </si>
+  <si>
+    <t>Daylight sensor</t>
+  </si>
+  <si>
+    <t>CK11</t>
+  </si>
+  <si>
+    <t>Wall TV / display location, commercial</t>
+  </si>
+  <si>
+    <t>CK12</t>
+  </si>
+  <si>
+    <t>Ceiling receptacle for projector</t>
+  </si>
+  <si>
+    <t>CK19</t>
+  </si>
+  <si>
+    <t>GFCI receptacle, old work</t>
+  </si>
+  <si>
+    <t>CK23</t>
+  </si>
+  <si>
+    <t>Wall TV location (power + HDMI)</t>
+  </si>
+  <si>
+    <t>CK24</t>
+  </si>
+  <si>
+    <t>Island / peninsula pop-up receptacle</t>
+  </si>
+  <si>
     <t>CS6</t>
   </si>
   <si>
@@ -716,6 +770,30 @@
     <t>Modular furniture feed</t>
   </si>
   <si>
+    <t>CW7</t>
+  </si>
+  <si>
+    <t>Welder / shop receptacle, 50A (NEMA 6-50)</t>
+  </si>
+  <si>
+    <t>CW13</t>
+  </si>
+  <si>
+    <t>Hospital-grade receptacle (exam / operatory)</t>
+  </si>
+  <si>
+    <t>CW14</t>
+  </si>
+  <si>
+    <t>208V kitchen equipment receptacle, 30A (NEMA 6-30)</t>
+  </si>
+  <si>
+    <t>CW15</t>
+  </si>
+  <si>
+    <t>Recessed clock receptacle</t>
+  </si>
+  <si>
     <t>DV6</t>
   </si>
   <si>
@@ -848,6 +926,48 @@
     <t>Bathroom 20A circuit</t>
   </si>
   <si>
+    <t>CK3</t>
+  </si>
+  <si>
+    <t>Water heater connection, commercial (208V, MC)</t>
+  </si>
+  <si>
+    <t>CK13</t>
+  </si>
+  <si>
+    <t>Mini-split connection, MC</t>
+  </si>
+  <si>
+    <t>CK14</t>
+  </si>
+  <si>
+    <t>Electric wall heater, fan-forced</t>
+  </si>
+  <si>
+    <t>CK18</t>
+  </si>
+  <si>
+    <t>Over-range microwave circuit, 20A</t>
+  </si>
+  <si>
+    <t>CK20</t>
+  </si>
+  <si>
+    <t>Wall oven or cooktop, hardwired 40A</t>
+  </si>
+  <si>
+    <t>CK21</t>
+  </si>
+  <si>
+    <t>Bath fan / heater combo, 20A</t>
+  </si>
+  <si>
+    <t>CK22</t>
+  </si>
+  <si>
+    <t>Heated bathroom floor</t>
+  </si>
+  <si>
     <t>CS3</t>
   </si>
   <si>
@@ -872,6 +992,36 @@
     <t>Kitchen hood shunt interface</t>
   </si>
   <si>
+    <t>CW1</t>
+  </si>
+  <si>
+    <t>Equipment connection, hardwired (flex whip), 208/240V</t>
+  </si>
+  <si>
+    <t>CW2</t>
+  </si>
+  <si>
+    <t>Commercial Level 2 EV charger, 208V</t>
+  </si>
+  <si>
+    <t>CW5</t>
+  </si>
+  <si>
+    <t>Overhead door operator connection</t>
+  </si>
+  <si>
+    <t>CW6</t>
+  </si>
+  <si>
+    <t>Air compressor connection, 240V</t>
+  </si>
+  <si>
+    <t>CW11</t>
+  </si>
+  <si>
+    <t>EV-ready conduit stub (EV-capable space)</t>
+  </si>
+  <si>
     <t>MH2</t>
   </si>
   <si>
@@ -1040,12 +1190,42 @@
     <t>Temporary lighting string, per 100 ft</t>
   </si>
   <si>
+    <t>CK1</t>
+  </si>
+  <si>
+    <t>Emergency light (bug-eye), standalone</t>
+  </si>
+  <si>
+    <t>CK4</t>
+  </si>
+  <si>
+    <t>Recessed wafer downlight, commercial (MC whip)</t>
+  </si>
+  <si>
+    <t>CK17</t>
+  </si>
+  <si>
+    <t>Ceiling light, old work</t>
+  </si>
+  <si>
+    <t>CK25</t>
+  </si>
+  <si>
+    <t>Pendant or sconce, old work</t>
+  </si>
+  <si>
     <t>CS2</t>
   </si>
   <si>
     <t>Time clock and lighting contactor</t>
   </si>
   <si>
+    <t>CW9</t>
+  </si>
+  <si>
+    <t>Bollard light</t>
+  </si>
+  <si>
     <t>GC1</t>
   </si>
   <si>
@@ -1178,6 +1358,36 @@
     <t>Recessed can retrofit, 4"</t>
   </si>
   <si>
+    <t>CK2</t>
+  </si>
+  <si>
+    <t>Fire alarm strobe only</t>
+  </si>
+  <si>
+    <t>CK5</t>
+  </si>
+  <si>
+    <t>Fire alarm control panel connection</t>
+  </si>
+  <si>
+    <t>CK9</t>
+  </si>
+  <si>
+    <t>Data drop, Cat6 2-port (commercial)</t>
+  </si>
+  <si>
+    <t>CK15</t>
+  </si>
+  <si>
+    <t>Fire alarm speaker/strobe</t>
+  </si>
+  <si>
+    <t>CK16</t>
+  </si>
+  <si>
+    <t>Heat detector</t>
+  </si>
+  <si>
     <t>CS11</t>
   </si>
   <si>
@@ -1202,6 +1412,12 @@
     <t>Duct smoke detector</t>
   </si>
   <si>
+    <t>CW8</t>
+  </si>
+  <si>
+    <t>Wireless access point drop (ceiling)</t>
+  </si>
+  <si>
     <t>MS7</t>
   </si>
   <si>
@@ -1244,6 +1460,36 @@
     <t>Video doorbell wiring</t>
   </si>
   <si>
+    <t>CK26</t>
+  </si>
+  <si>
+    <t>Tandem breaker add</t>
+  </si>
+  <si>
+    <t>CW3</t>
+  </si>
+  <si>
+    <t>Outdoor emergency service disconnect (NEC 230.85)</t>
+  </si>
+  <si>
+    <t>CW4</t>
+  </si>
+  <si>
+    <t>Apartment unit panel, 125A main-lug</t>
+  </si>
+  <si>
+    <t>CW10</t>
+  </si>
+  <si>
+    <t>Manual transfer switch, 6–10 circuit</t>
+  </si>
+  <si>
+    <t>CW12</t>
+  </si>
+  <si>
+    <t>Multi-unit meter center</t>
+  </si>
+  <si>
     <t>GC2</t>
   </si>
   <si>
@@ -1376,7 +1622,7 @@
     <t>Your top-30 commercial list, then the top-30 residential list (references/top-assemblies-draft.md), then every other starter by category.</t>
   </si>
   <si>
-    <t>0 rows say NEW: starters added since the version this was compared with (assembly-hours-prev.xlsx). Filter the 'New' column to see only them.</t>
+    <t>Not marked in this build.</t>
   </si>
   <si>
     <t>HELD</t>
@@ -1787,7 +2033,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J226"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3473,7 +3719,7 @@
         <v>201</v>
       </c>
       <c r="D79" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E79" t="s">
         <v>234</v>
@@ -3494,7 +3740,7 @@
         <v>201</v>
       </c>
       <c r="D80" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E80" t="s">
         <v>236</v>
@@ -3536,7 +3782,7 @@
         <v>201</v>
       </c>
       <c r="D82" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E82" t="s">
         <v>240</v>
@@ -3557,7 +3803,7 @@
         <v>201</v>
       </c>
       <c r="D83" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E83" t="s">
         <v>242</v>
@@ -3578,7 +3824,7 @@
         <v>201</v>
       </c>
       <c r="D84" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E84" t="s">
         <v>244</v>
@@ -3599,7 +3845,7 @@
         <v>201</v>
       </c>
       <c r="D85" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E85" t="s">
         <v>246</v>
@@ -3620,7 +3866,7 @@
         <v>201</v>
       </c>
       <c r="D86" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E86" t="s">
         <v>248</v>
@@ -3641,7 +3887,7 @@
         <v>201</v>
       </c>
       <c r="D87" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E87" t="s">
         <v>250</v>
@@ -3662,7 +3908,7 @@
         <v>201</v>
       </c>
       <c r="D88" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="E88" t="s">
         <v>252</v>
@@ -3683,7 +3929,7 @@
         <v>201</v>
       </c>
       <c r="D89" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E89" t="s">
         <v>254</v>
@@ -3746,7 +3992,7 @@
         <v>201</v>
       </c>
       <c r="D92" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E92" t="s">
         <v>260</v>
@@ -3767,7 +4013,7 @@
         <v>201</v>
       </c>
       <c r="D93" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E93" t="s">
         <v>262</v>
@@ -3788,7 +4034,7 @@
         <v>201</v>
       </c>
       <c r="D94" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E94" t="s">
         <v>264</v>
@@ -3809,7 +4055,7 @@
         <v>201</v>
       </c>
       <c r="D95" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E95" t="s">
         <v>266</v>
@@ -3830,7 +4076,7 @@
         <v>201</v>
       </c>
       <c r="D96" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E96" t="s">
         <v>268</v>
@@ -3851,7 +4097,7 @@
         <v>201</v>
       </c>
       <c r="D97" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E97" t="s">
         <v>270</v>
@@ -3872,7 +4118,7 @@
         <v>201</v>
       </c>
       <c r="D98" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="E98" t="s">
         <v>272</v>
@@ -3893,7 +4139,7 @@
         <v>201</v>
       </c>
       <c r="D99" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="E99" t="s">
         <v>274</v>
@@ -3914,7 +4160,7 @@
         <v>201</v>
       </c>
       <c r="D100" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="E100" t="s">
         <v>276</v>
@@ -3935,13 +4181,13 @@
         <v>201</v>
       </c>
       <c r="D101" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E101" t="s">
         <v>278</v>
       </c>
       <c r="F101" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G101" t="s">
         <v>279</v>
@@ -3956,13 +4202,13 @@
         <v>201</v>
       </c>
       <c r="D102" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E102" t="s">
         <v>280</v>
       </c>
       <c r="F102" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G102" t="s">
         <v>281</v>
@@ -3983,7 +4229,7 @@
         <v>282</v>
       </c>
       <c r="F103" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G103" t="s">
         <v>283</v>
@@ -4004,7 +4250,7 @@
         <v>284</v>
       </c>
       <c r="F104" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G104" t="s">
         <v>285</v>
@@ -4019,13 +4265,13 @@
         <v>201</v>
       </c>
       <c r="D105" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E105" t="s">
         <v>286</v>
       </c>
       <c r="F105" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G105" t="s">
         <v>287</v>
@@ -4040,13 +4286,13 @@
         <v>201</v>
       </c>
       <c r="D106" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E106" t="s">
         <v>288</v>
       </c>
       <c r="F106" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G106" t="s">
         <v>289</v>
@@ -4061,13 +4307,13 @@
         <v>201</v>
       </c>
       <c r="D107" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E107" t="s">
         <v>290</v>
       </c>
       <c r="F107" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G107" t="s">
         <v>291</v>
@@ -4088,7 +4334,7 @@
         <v>292</v>
       </c>
       <c r="F108" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G108" t="s">
         <v>293</v>
@@ -4109,7 +4355,7 @@
         <v>294</v>
       </c>
       <c r="F109" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G109" t="s">
         <v>295</v>
@@ -4130,7 +4376,7 @@
         <v>296</v>
       </c>
       <c r="F110" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G110" t="s">
         <v>297</v>
@@ -4145,13 +4391,13 @@
         <v>201</v>
       </c>
       <c r="D111" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E111" t="s">
         <v>298</v>
       </c>
       <c r="F111" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G111" t="s">
         <v>299</v>
@@ -4166,13 +4412,13 @@
         <v>201</v>
       </c>
       <c r="D112" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E112" t="s">
         <v>300</v>
       </c>
       <c r="F112" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G112" t="s">
         <v>301</v>
@@ -4187,13 +4433,13 @@
         <v>201</v>
       </c>
       <c r="D113" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E113" t="s">
         <v>302</v>
       </c>
       <c r="F113" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="G113" t="s">
         <v>303</v>
@@ -4229,7 +4475,7 @@
         <v>201</v>
       </c>
       <c r="D115" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E115" t="s">
         <v>306</v>
@@ -4355,7 +4601,7 @@
         <v>201</v>
       </c>
       <c r="D121" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E121" t="s">
         <v>318</v>
@@ -4376,7 +4622,7 @@
         <v>201</v>
       </c>
       <c r="D122" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E122" t="s">
         <v>320</v>
@@ -4397,7 +4643,7 @@
         <v>201</v>
       </c>
       <c r="D123" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E123" t="s">
         <v>322</v>
@@ -4418,7 +4664,7 @@
         <v>201</v>
       </c>
       <c r="D124" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E124" t="s">
         <v>324</v>
@@ -4445,7 +4691,7 @@
         <v>326</v>
       </c>
       <c r="F125" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G125" t="s">
         <v>327</v>
@@ -4460,13 +4706,13 @@
         <v>201</v>
       </c>
       <c r="D126" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E126" t="s">
         <v>328</v>
       </c>
       <c r="F126" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G126" t="s">
         <v>329</v>
@@ -4487,7 +4733,7 @@
         <v>330</v>
       </c>
       <c r="F127" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G127" t="s">
         <v>331</v>
@@ -4508,7 +4754,7 @@
         <v>332</v>
       </c>
       <c r="F128" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G128" t="s">
         <v>333</v>
@@ -4523,13 +4769,13 @@
         <v>201</v>
       </c>
       <c r="D129" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E129" t="s">
         <v>334</v>
       </c>
       <c r="F129" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G129" t="s">
         <v>335</v>
@@ -4550,7 +4796,7 @@
         <v>336</v>
       </c>
       <c r="F130" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G130" t="s">
         <v>337</v>
@@ -4565,13 +4811,13 @@
         <v>201</v>
       </c>
       <c r="D131" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E131" t="s">
         <v>338</v>
       </c>
       <c r="F131" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G131" t="s">
         <v>339</v>
@@ -4586,13 +4832,13 @@
         <v>201</v>
       </c>
       <c r="D132" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E132" t="s">
         <v>340</v>
       </c>
       <c r="F132" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="G132" t="s">
         <v>341</v>
@@ -4613,7 +4859,7 @@
         <v>342</v>
       </c>
       <c r="F133" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G133" t="s">
         <v>343</v>
@@ -4634,7 +4880,7 @@
         <v>344</v>
       </c>
       <c r="F134" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G134" t="s">
         <v>345</v>
@@ -4655,7 +4901,7 @@
         <v>346</v>
       </c>
       <c r="F135" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G135" t="s">
         <v>347</v>
@@ -4676,7 +4922,7 @@
         <v>348</v>
       </c>
       <c r="F136" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G136" t="s">
         <v>349</v>
@@ -4691,13 +4937,13 @@
         <v>201</v>
       </c>
       <c r="D137" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E137" t="s">
         <v>350</v>
       </c>
       <c r="F137" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G137" t="s">
         <v>351</v>
@@ -4712,13 +4958,13 @@
         <v>201</v>
       </c>
       <c r="D138" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E138" t="s">
         <v>352</v>
       </c>
       <c r="F138" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G138" t="s">
         <v>353</v>
@@ -4733,13 +4979,13 @@
         <v>201</v>
       </c>
       <c r="D139" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E139" t="s">
         <v>354</v>
       </c>
       <c r="F139" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G139" t="s">
         <v>355</v>
@@ -4754,13 +5000,13 @@
         <v>201</v>
       </c>
       <c r="D140" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E140" t="s">
         <v>356</v>
       </c>
       <c r="F140" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G140" t="s">
         <v>357</v>
@@ -4775,13 +5021,13 @@
         <v>201</v>
       </c>
       <c r="D141" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="E141" t="s">
         <v>358</v>
       </c>
       <c r="F141" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G141" t="s">
         <v>359</v>
@@ -4802,7 +5048,7 @@
         <v>360</v>
       </c>
       <c r="F142" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G142" t="s">
         <v>361</v>
@@ -4823,7 +5069,7 @@
         <v>362</v>
       </c>
       <c r="F143" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G143" t="s">
         <v>363</v>
@@ -4844,7 +5090,7 @@
         <v>364</v>
       </c>
       <c r="F144" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G144" t="s">
         <v>365</v>
@@ -4859,13 +5105,13 @@
         <v>201</v>
       </c>
       <c r="D145" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E145" t="s">
         <v>366</v>
       </c>
       <c r="F145" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G145" t="s">
         <v>367</v>
@@ -4886,7 +5132,7 @@
         <v>368</v>
       </c>
       <c r="F146" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G146" t="s">
         <v>369</v>
@@ -4907,7 +5153,7 @@
         <v>370</v>
       </c>
       <c r="F147" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G147" t="s">
         <v>371</v>
@@ -4922,13 +5168,13 @@
         <v>201</v>
       </c>
       <c r="D148" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E148" t="s">
         <v>372</v>
       </c>
       <c r="F148" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G148" t="s">
         <v>373</v>
@@ -4943,13 +5189,13 @@
         <v>201</v>
       </c>
       <c r="D149" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E149" t="s">
         <v>374</v>
       </c>
       <c r="F149" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G149" t="s">
         <v>375</v>
@@ -4970,7 +5216,7 @@
         <v>376</v>
       </c>
       <c r="F150" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G150" t="s">
         <v>377</v>
@@ -4985,13 +5231,13 @@
         <v>201</v>
       </c>
       <c r="D151" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E151" t="s">
         <v>378</v>
       </c>
       <c r="F151" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G151" t="s">
         <v>379</v>
@@ -5012,7 +5258,7 @@
         <v>380</v>
       </c>
       <c r="F152" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G152" t="s">
         <v>381</v>
@@ -5033,7 +5279,7 @@
         <v>382</v>
       </c>
       <c r="F153" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G153" t="s">
         <v>383</v>
@@ -5048,13 +5294,13 @@
         <v>201</v>
       </c>
       <c r="D154" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E154" t="s">
         <v>384</v>
       </c>
       <c r="F154" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G154" t="s">
         <v>385</v>
@@ -5069,13 +5315,13 @@
         <v>201</v>
       </c>
       <c r="D155" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E155" t="s">
         <v>386</v>
       </c>
       <c r="F155" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="G155" t="s">
         <v>387</v>
@@ -5090,13 +5336,13 @@
         <v>201</v>
       </c>
       <c r="D156" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E156" t="s">
         <v>388</v>
       </c>
       <c r="F156" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="G156" t="s">
         <v>389</v>
@@ -5111,13 +5357,13 @@
         <v>201</v>
       </c>
       <c r="D157" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E157" t="s">
         <v>390</v>
       </c>
       <c r="F157" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="G157" t="s">
         <v>391</v>
@@ -5138,7 +5384,7 @@
         <v>392</v>
       </c>
       <c r="F158" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G158" t="s">
         <v>393</v>
@@ -5159,7 +5405,7 @@
         <v>394</v>
       </c>
       <c r="F159" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G159" t="s">
         <v>395</v>
@@ -5180,7 +5426,7 @@
         <v>396</v>
       </c>
       <c r="F160" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G160" t="s">
         <v>397</v>
@@ -5201,7 +5447,7 @@
         <v>398</v>
       </c>
       <c r="F161" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G161" t="s">
         <v>399</v>
@@ -5216,13 +5462,13 @@
         <v>201</v>
       </c>
       <c r="D162" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E162" t="s">
         <v>400</v>
       </c>
       <c r="F162" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G162" t="s">
         <v>401</v>
@@ -5237,13 +5483,13 @@
         <v>201</v>
       </c>
       <c r="D163" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E163" t="s">
         <v>402</v>
       </c>
       <c r="F163" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G163" t="s">
         <v>403</v>
@@ -5264,7 +5510,7 @@
         <v>404</v>
       </c>
       <c r="F164" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G164" t="s">
         <v>405</v>
@@ -5279,13 +5525,13 @@
         <v>201</v>
       </c>
       <c r="D165" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E165" t="s">
         <v>406</v>
       </c>
       <c r="F165" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G165" t="s">
         <v>407</v>
@@ -5300,13 +5546,13 @@
         <v>201</v>
       </c>
       <c r="D166" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E166" t="s">
         <v>408</v>
       </c>
       <c r="F166" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="G166" t="s">
         <v>409</v>
@@ -5321,13 +5567,13 @@
         <v>201</v>
       </c>
       <c r="D167" t="s">
-        <v>12</v>
+        <v>138</v>
       </c>
       <c r="E167" t="s">
         <v>410</v>
       </c>
       <c r="F167" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G167" t="s">
         <v>411</v>
@@ -5342,13 +5588,13 @@
         <v>201</v>
       </c>
       <c r="D168" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="E168" t="s">
         <v>412</v>
       </c>
       <c r="F168" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G168" t="s">
         <v>413</v>
@@ -5363,13 +5609,13 @@
         <v>201</v>
       </c>
       <c r="D169" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="E169" t="s">
         <v>414</v>
       </c>
       <c r="F169" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G169" t="s">
         <v>415</v>
@@ -5384,13 +5630,13 @@
         <v>201</v>
       </c>
       <c r="D170" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="E170" t="s">
         <v>416</v>
       </c>
       <c r="F170" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G170" t="s">
         <v>417</v>
@@ -5411,7 +5657,7 @@
         <v>418</v>
       </c>
       <c r="F171" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G171" t="s">
         <v>419</v>
@@ -5426,19 +5672,16 @@
         <v>201</v>
       </c>
       <c r="D172" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E172" t="s">
         <v>420</v>
       </c>
       <c r="F172" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G172" t="s">
         <v>421</v>
-      </c>
-      <c r="H172">
-        <v>8</v>
       </c>
       <c r="I172" s="3"/>
     </row>
@@ -5450,13 +5693,13 @@
         <v>201</v>
       </c>
       <c r="D173" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E173" t="s">
         <v>422</v>
       </c>
       <c r="F173" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G173" t="s">
         <v>423</v>
@@ -5477,7 +5720,7 @@
         <v>424</v>
       </c>
       <c r="F174" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G174" t="s">
         <v>425</v>
@@ -5498,7 +5741,7 @@
         <v>426</v>
       </c>
       <c r="F175" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G175" t="s">
         <v>427</v>
@@ -5513,13 +5756,13 @@
         <v>201</v>
       </c>
       <c r="D176" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="E176" t="s">
         <v>428</v>
       </c>
       <c r="F176" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G176" t="s">
         <v>429</v>
@@ -5540,7 +5783,7 @@
         <v>430</v>
       </c>
       <c r="F177" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G177" t="s">
         <v>431</v>
@@ -5555,13 +5798,13 @@
         <v>201</v>
       </c>
       <c r="D178" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="E178" t="s">
         <v>432</v>
       </c>
       <c r="F178" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G178" t="s">
         <v>433</v>
@@ -5582,7 +5825,7 @@
         <v>434</v>
       </c>
       <c r="F179" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G179" t="s">
         <v>435</v>
@@ -5603,7 +5846,7 @@
         <v>436</v>
       </c>
       <c r="F180" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G180" t="s">
         <v>437</v>
@@ -5624,7 +5867,7 @@
         <v>438</v>
       </c>
       <c r="F181" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G181" t="s">
         <v>439</v>
@@ -5645,7 +5888,7 @@
         <v>440</v>
       </c>
       <c r="F182" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G182" t="s">
         <v>441</v>
@@ -5666,7 +5909,7 @@
         <v>442</v>
       </c>
       <c r="F183" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G183" t="s">
         <v>443</v>
@@ -5681,13 +5924,13 @@
         <v>201</v>
       </c>
       <c r="D184" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="E184" t="s">
         <v>444</v>
       </c>
       <c r="F184" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G184" t="s">
         <v>445</v>
@@ -5708,12 +5951,876 @@
         <v>446</v>
       </c>
       <c r="F185" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="G185" t="s">
         <v>447</v>
       </c>
       <c r="I185" s="3"/>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="C186" t="s">
+        <v>201</v>
+      </c>
+      <c r="D186" t="s">
+        <v>12</v>
+      </c>
+      <c r="E186" t="s">
+        <v>448</v>
+      </c>
+      <c r="F186" t="s">
+        <v>89</v>
+      </c>
+      <c r="G186" t="s">
+        <v>449</v>
+      </c>
+      <c r="I186" s="3"/>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="C187" t="s">
+        <v>201</v>
+      </c>
+      <c r="D187" t="s">
+        <v>12</v>
+      </c>
+      <c r="E187" t="s">
+        <v>450</v>
+      </c>
+      <c r="F187" t="s">
+        <v>89</v>
+      </c>
+      <c r="G187" t="s">
+        <v>451</v>
+      </c>
+      <c r="I187" s="3"/>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="C188" t="s">
+        <v>201</v>
+      </c>
+      <c r="D188" t="s">
+        <v>12</v>
+      </c>
+      <c r="E188" t="s">
+        <v>452</v>
+      </c>
+      <c r="F188" t="s">
+        <v>89</v>
+      </c>
+      <c r="G188" t="s">
+        <v>453</v>
+      </c>
+      <c r="I188" s="3"/>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="C189" t="s">
+        <v>201</v>
+      </c>
+      <c r="D189" t="s">
+        <v>12</v>
+      </c>
+      <c r="E189" t="s">
+        <v>454</v>
+      </c>
+      <c r="F189" t="s">
+        <v>89</v>
+      </c>
+      <c r="G189" t="s">
+        <v>455</v>
+      </c>
+      <c r="I189" s="3"/>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="C190" t="s">
+        <v>201</v>
+      </c>
+      <c r="D190" t="s">
+        <v>12</v>
+      </c>
+      <c r="E190" t="s">
+        <v>456</v>
+      </c>
+      <c r="F190" t="s">
+        <v>89</v>
+      </c>
+      <c r="G190" t="s">
+        <v>457</v>
+      </c>
+      <c r="I190" s="3"/>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="C191" t="s">
+        <v>201</v>
+      </c>
+      <c r="D191" t="s">
+        <v>12</v>
+      </c>
+      <c r="E191" t="s">
+        <v>458</v>
+      </c>
+      <c r="F191" t="s">
+        <v>89</v>
+      </c>
+      <c r="G191" t="s">
+        <v>459</v>
+      </c>
+      <c r="I191" s="3"/>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="C192" t="s">
+        <v>201</v>
+      </c>
+      <c r="D192" t="s">
+        <v>12</v>
+      </c>
+      <c r="E192" t="s">
+        <v>460</v>
+      </c>
+      <c r="F192" t="s">
+        <v>89</v>
+      </c>
+      <c r="G192" t="s">
+        <v>461</v>
+      </c>
+      <c r="I192" s="3"/>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="C193" t="s">
+        <v>201</v>
+      </c>
+      <c r="D193" t="s">
+        <v>12</v>
+      </c>
+      <c r="E193" t="s">
+        <v>462</v>
+      </c>
+      <c r="F193" t="s">
+        <v>89</v>
+      </c>
+      <c r="G193" t="s">
+        <v>463</v>
+      </c>
+      <c r="I193" s="3"/>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="C194" t="s">
+        <v>201</v>
+      </c>
+      <c r="D194" t="s">
+        <v>12</v>
+      </c>
+      <c r="E194" t="s">
+        <v>464</v>
+      </c>
+      <c r="F194" t="s">
+        <v>89</v>
+      </c>
+      <c r="G194" t="s">
+        <v>465</v>
+      </c>
+      <c r="I194" s="3"/>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="C195" t="s">
+        <v>201</v>
+      </c>
+      <c r="D195" t="s">
+        <v>12</v>
+      </c>
+      <c r="E195" t="s">
+        <v>466</v>
+      </c>
+      <c r="F195" t="s">
+        <v>89</v>
+      </c>
+      <c r="G195" t="s">
+        <v>467</v>
+      </c>
+      <c r="I195" s="3"/>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="C196" t="s">
+        <v>201</v>
+      </c>
+      <c r="D196" t="s">
+        <v>138</v>
+      </c>
+      <c r="E196" t="s">
+        <v>468</v>
+      </c>
+      <c r="F196" t="s">
+        <v>89</v>
+      </c>
+      <c r="G196" t="s">
+        <v>469</v>
+      </c>
+      <c r="I196" s="3"/>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="C197" t="s">
+        <v>201</v>
+      </c>
+      <c r="D197" t="s">
+        <v>138</v>
+      </c>
+      <c r="E197" t="s">
+        <v>470</v>
+      </c>
+      <c r="F197" t="s">
+        <v>89</v>
+      </c>
+      <c r="G197" t="s">
+        <v>471</v>
+      </c>
+      <c r="I197" s="3"/>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="C198" t="s">
+        <v>201</v>
+      </c>
+      <c r="D198" t="s">
+        <v>53</v>
+      </c>
+      <c r="E198" t="s">
+        <v>472</v>
+      </c>
+      <c r="F198" t="s">
+        <v>89</v>
+      </c>
+      <c r="G198" t="s">
+        <v>473</v>
+      </c>
+      <c r="I198" s="3"/>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="C199" t="s">
+        <v>201</v>
+      </c>
+      <c r="D199" t="s">
+        <v>138</v>
+      </c>
+      <c r="E199" t="s">
+        <v>474</v>
+      </c>
+      <c r="F199" t="s">
+        <v>89</v>
+      </c>
+      <c r="G199" t="s">
+        <v>475</v>
+      </c>
+      <c r="I199" s="3"/>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="C200" t="s">
+        <v>201</v>
+      </c>
+      <c r="D200" t="s">
+        <v>12</v>
+      </c>
+      <c r="E200" t="s">
+        <v>476</v>
+      </c>
+      <c r="F200" t="s">
+        <v>89</v>
+      </c>
+      <c r="G200" t="s">
+        <v>477</v>
+      </c>
+      <c r="I200" s="3"/>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="C201" t="s">
+        <v>201</v>
+      </c>
+      <c r="D201" t="s">
+        <v>138</v>
+      </c>
+      <c r="E201" t="s">
+        <v>478</v>
+      </c>
+      <c r="F201" t="s">
+        <v>89</v>
+      </c>
+      <c r="G201" t="s">
+        <v>479</v>
+      </c>
+      <c r="I201" s="3"/>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="C202" t="s">
+        <v>201</v>
+      </c>
+      <c r="D202" t="s">
+        <v>138</v>
+      </c>
+      <c r="E202" t="s">
+        <v>480</v>
+      </c>
+      <c r="F202" t="s">
+        <v>89</v>
+      </c>
+      <c r="G202" t="s">
+        <v>481</v>
+      </c>
+      <c r="I202" s="3"/>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="C203" t="s">
+        <v>201</v>
+      </c>
+      <c r="D203" t="s">
+        <v>138</v>
+      </c>
+      <c r="E203" t="s">
+        <v>482</v>
+      </c>
+      <c r="F203" t="s">
+        <v>85</v>
+      </c>
+      <c r="G203" t="s">
+        <v>483</v>
+      </c>
+      <c r="I203" s="3"/>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="C204" t="s">
+        <v>201</v>
+      </c>
+      <c r="D204" t="s">
+        <v>138</v>
+      </c>
+      <c r="E204" t="s">
+        <v>484</v>
+      </c>
+      <c r="F204" t="s">
+        <v>85</v>
+      </c>
+      <c r="G204" t="s">
+        <v>485</v>
+      </c>
+      <c r="I204" s="3"/>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="C205" t="s">
+        <v>201</v>
+      </c>
+      <c r="D205" t="s">
+        <v>138</v>
+      </c>
+      <c r="E205" t="s">
+        <v>486</v>
+      </c>
+      <c r="F205" t="s">
+        <v>85</v>
+      </c>
+      <c r="G205" t="s">
+        <v>487</v>
+      </c>
+      <c r="I205" s="3"/>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="C206" t="s">
+        <v>201</v>
+      </c>
+      <c r="D206" t="s">
+        <v>138</v>
+      </c>
+      <c r="E206" t="s">
+        <v>488</v>
+      </c>
+      <c r="F206" t="s">
+        <v>85</v>
+      </c>
+      <c r="G206" t="s">
+        <v>489</v>
+      </c>
+      <c r="I206" s="3"/>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="C207" t="s">
+        <v>201</v>
+      </c>
+      <c r="D207" t="s">
+        <v>53</v>
+      </c>
+      <c r="E207" t="s">
+        <v>490</v>
+      </c>
+      <c r="F207" t="s">
+        <v>85</v>
+      </c>
+      <c r="G207" t="s">
+        <v>491</v>
+      </c>
+      <c r="I207" s="3"/>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="C208" t="s">
+        <v>201</v>
+      </c>
+      <c r="D208" t="s">
+        <v>12</v>
+      </c>
+      <c r="E208" t="s">
+        <v>492</v>
+      </c>
+      <c r="F208" t="s">
+        <v>85</v>
+      </c>
+      <c r="G208" t="s">
+        <v>493</v>
+      </c>
+      <c r="I208" s="3"/>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="C209" t="s">
+        <v>201</v>
+      </c>
+      <c r="D209" t="s">
+        <v>138</v>
+      </c>
+      <c r="E209" t="s">
+        <v>494</v>
+      </c>
+      <c r="F209" t="s">
+        <v>85</v>
+      </c>
+      <c r="G209" t="s">
+        <v>495</v>
+      </c>
+      <c r="I209" s="3"/>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="C210" t="s">
+        <v>201</v>
+      </c>
+      <c r="D210" t="s">
+        <v>138</v>
+      </c>
+      <c r="E210" t="s">
+        <v>496</v>
+      </c>
+      <c r="F210" t="s">
+        <v>85</v>
+      </c>
+      <c r="G210" t="s">
+        <v>497</v>
+      </c>
+      <c r="I210" s="3"/>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="C211" t="s">
+        <v>201</v>
+      </c>
+      <c r="D211" t="s">
+        <v>138</v>
+      </c>
+      <c r="E211" t="s">
+        <v>498</v>
+      </c>
+      <c r="F211" t="s">
+        <v>85</v>
+      </c>
+      <c r="G211" t="s">
+        <v>499</v>
+      </c>
+      <c r="I211" s="3"/>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="C212" t="s">
+        <v>201</v>
+      </c>
+      <c r="D212" t="s">
+        <v>138</v>
+      </c>
+      <c r="E212" t="s">
+        <v>500</v>
+      </c>
+      <c r="F212" t="s">
+        <v>85</v>
+      </c>
+      <c r="G212" t="s">
+        <v>501</v>
+      </c>
+      <c r="I212" s="3"/>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="C213" t="s">
+        <v>201</v>
+      </c>
+      <c r="D213" t="s">
+        <v>53</v>
+      </c>
+      <c r="E213" t="s">
+        <v>502</v>
+      </c>
+      <c r="F213" t="s">
+        <v>85</v>
+      </c>
+      <c r="G213" t="s">
+        <v>503</v>
+      </c>
+      <c r="H213">
+        <v>8</v>
+      </c>
+      <c r="I213" s="3"/>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="C214" t="s">
+        <v>201</v>
+      </c>
+      <c r="D214" t="s">
+        <v>53</v>
+      </c>
+      <c r="E214" t="s">
+        <v>504</v>
+      </c>
+      <c r="F214" t="s">
+        <v>85</v>
+      </c>
+      <c r="G214" t="s">
+        <v>505</v>
+      </c>
+      <c r="I214" s="3"/>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="C215" t="s">
+        <v>201</v>
+      </c>
+      <c r="D215" t="s">
+        <v>138</v>
+      </c>
+      <c r="E215" t="s">
+        <v>506</v>
+      </c>
+      <c r="F215" t="s">
+        <v>85</v>
+      </c>
+      <c r="G215" t="s">
+        <v>507</v>
+      </c>
+      <c r="I215" s="3"/>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="C216" t="s">
+        <v>201</v>
+      </c>
+      <c r="D216" t="s">
+        <v>53</v>
+      </c>
+      <c r="E216" t="s">
+        <v>508</v>
+      </c>
+      <c r="F216" t="s">
+        <v>85</v>
+      </c>
+      <c r="G216" t="s">
+        <v>509</v>
+      </c>
+      <c r="I216" s="3"/>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="C217" t="s">
+        <v>201</v>
+      </c>
+      <c r="D217" t="s">
+        <v>53</v>
+      </c>
+      <c r="E217" t="s">
+        <v>510</v>
+      </c>
+      <c r="F217" t="s">
+        <v>85</v>
+      </c>
+      <c r="G217" t="s">
+        <v>511</v>
+      </c>
+      <c r="I217" s="3"/>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="C218" t="s">
+        <v>201</v>
+      </c>
+      <c r="D218" t="s">
+        <v>138</v>
+      </c>
+      <c r="E218" t="s">
+        <v>512</v>
+      </c>
+      <c r="F218" t="s">
+        <v>85</v>
+      </c>
+      <c r="G218" t="s">
+        <v>513</v>
+      </c>
+      <c r="I218" s="3"/>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="C219" t="s">
+        <v>201</v>
+      </c>
+      <c r="D219" t="s">
+        <v>53</v>
+      </c>
+      <c r="E219" t="s">
+        <v>514</v>
+      </c>
+      <c r="F219" t="s">
+        <v>85</v>
+      </c>
+      <c r="G219" t="s">
+        <v>515</v>
+      </c>
+      <c r="I219" s="3"/>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="C220" t="s">
+        <v>201</v>
+      </c>
+      <c r="D220" t="s">
+        <v>12</v>
+      </c>
+      <c r="E220" t="s">
+        <v>516</v>
+      </c>
+      <c r="F220" t="s">
+        <v>85</v>
+      </c>
+      <c r="G220" t="s">
+        <v>517</v>
+      </c>
+      <c r="I220" s="3"/>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="C221" t="s">
+        <v>201</v>
+      </c>
+      <c r="D221" t="s">
+        <v>12</v>
+      </c>
+      <c r="E221" t="s">
+        <v>518</v>
+      </c>
+      <c r="F221" t="s">
+        <v>85</v>
+      </c>
+      <c r="G221" t="s">
+        <v>519</v>
+      </c>
+      <c r="I221" s="3"/>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="C222" t="s">
+        <v>201</v>
+      </c>
+      <c r="D222" t="s">
+        <v>12</v>
+      </c>
+      <c r="E222" t="s">
+        <v>520</v>
+      </c>
+      <c r="F222" t="s">
+        <v>85</v>
+      </c>
+      <c r="G222" t="s">
+        <v>521</v>
+      </c>
+      <c r="I222" s="3"/>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="C223" t="s">
+        <v>201</v>
+      </c>
+      <c r="D223" t="s">
+        <v>12</v>
+      </c>
+      <c r="E223" t="s">
+        <v>522</v>
+      </c>
+      <c r="F223" t="s">
+        <v>85</v>
+      </c>
+      <c r="G223" t="s">
+        <v>523</v>
+      </c>
+      <c r="I223" s="3"/>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="C224" t="s">
+        <v>201</v>
+      </c>
+      <c r="D224" t="s">
+        <v>53</v>
+      </c>
+      <c r="E224" t="s">
+        <v>524</v>
+      </c>
+      <c r="F224" t="s">
+        <v>85</v>
+      </c>
+      <c r="G224" t="s">
+        <v>525</v>
+      </c>
+      <c r="I224" s="3"/>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="C225" t="s">
+        <v>201</v>
+      </c>
+      <c r="D225" t="s">
+        <v>12</v>
+      </c>
+      <c r="E225" t="s">
+        <v>526</v>
+      </c>
+      <c r="F225" t="s">
+        <v>85</v>
+      </c>
+      <c r="G225" t="s">
+        <v>527</v>
+      </c>
+      <c r="I225" s="3"/>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="C226" t="s">
+        <v>201</v>
+      </c>
+      <c r="D226" t="s">
+        <v>53</v>
+      </c>
+      <c r="E226" t="s">
+        <v>528</v>
+      </c>
+      <c r="F226" t="s">
+        <v>85</v>
+      </c>
+      <c r="G226" t="s">
+        <v>529</v>
+      </c>
+      <c r="I226" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:J2"/>
@@ -5721,10 +6828,10 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I10:I185">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I10:I226">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I3:I185">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" error="Hours are a number above 0 — leave it blank to keep what ships." sqref="I3:I226">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -5744,26 +6851,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>448</v>
+        <v>530</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>449</v>
+        <v>531</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>450</v>
+        <v>532</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>451</v>
+        <v>533</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>452</v>
+        <v>534</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>453</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -5771,31 +6878,31 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>454</v>
+        <v>536</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>455</v>
+        <v>537</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>456</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>457</v>
+        <v>539</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>458</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>459</v>
+        <v>541</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>460</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>
